--- a/TFG_MODELOS_SIMPLES_MEJORADO/02_datasets/metadata/METADATA.xlsx
+++ b/TFG_MODELOS_SIMPLES_MEJORADO/02_datasets/metadata/METADATA.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="1062">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="904">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -1524,682 +1524,208 @@
     <t xml:space="preserve">Heartbleed</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992326 ± 0.000240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992297 ± 0.000252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992302 ± 0.000246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815281 ± 0.051810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772152 ± 0.034412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783326 ± 0.037294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.974495 ± 0.000803</t>
+    <t xml:space="preserve">0.960031 ± 0.000755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982078 ± 0.000699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969071 ± 0.000693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510063 ± 0.008061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894150 ± 0.011300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582772 ± 0.005066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885895 ± 0.001867</t>
   </si>
   <si>
     <t xml:space="preserve">nan ± nan</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919065 ± 0.000629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900552 ± 0.000669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906837 ± 0.000614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.219441 ± 0.000705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.185150 ± 0.000517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.198793 ± 0.000507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703268 ± 0.002422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975354 ± 0.000727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975130 ± 0.002210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.974745 ± 0.001078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647390 ± 0.052748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581735 ± 0.046975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600376 ± 0.041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917793 ± 0.003142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934584 ± 0.001599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977044 ± 0.000704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952251 ± 0.001360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473722 ± 0.023960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876084 ± 0.035912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547356 ± 0.024651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828299 ± 0.003357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487698 ± 0.009611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929549 ± 0.002487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603224 ± 0.010709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.219219 ± 0.004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634468 ± 0.021947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.227191 ± 0.004857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374889 ± 0.004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813276 ± 0.025072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951256 ± 0.000673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.865086 ± 0.016697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319469 ± 0.015324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885624 ± 0.031685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391654 ± 0.021857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642402 ± 0.026834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161415 ± 0.019790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898126 ± 0.016943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.178678 ± 0.017318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.202789 ± 0.013736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768352 ± 0.030354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162555 ± 0.026350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.207596 ± 0.035071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112858 ± 0.006727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554813 ± 0.175873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138910 ± 0.013129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125586 ± 0.015933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549319 ± 0.062581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.117366 ± 0.009716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.048359 ± 0.051059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.169962 ± 0.028952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833498 ± 0.045446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173945 ± 0.020811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.182905 ± 0.012641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791518 ± 0.031211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157261 ± 0.028268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.203333 ± 0.036111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.940117 ± 0.001285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978613 ± 0.000860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956277 ± 0.001260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487292 ± 0.024486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876943 ± 0.032945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557238 ± 0.023244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839277 ± 0.002815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497112 ± 0.008355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936342 ± 0.002337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614428 ± 0.008137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.226888 ± 0.002453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.679912 ± 0.023729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.237150 ± 0.001667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383628 ± 0.003248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841360 ± 0.010889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956355 ± 0.002757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886086 ± 0.007047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331936 ± 0.015894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895569 ± 0.007081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405593 ± 0.019648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.674891 ± 0.013473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161168 ± 0.020046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893931 ± 0.016134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.178143 ± 0.017767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.206878 ± 0.015265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768955 ± 0.032696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167730 ± 0.028072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.207539 ± 0.035187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113927 ± 0.006667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553839 ± 0.180879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141256 ± 0.012499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128732 ± 0.015743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546964 ± 0.073708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.120375 ± 0.010968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.048987 ± 0.050397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170967 ± 0.031012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833345 ± 0.042728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176001 ± 0.031609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.198810 ± 0.038956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791551 ± 0.030625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.172210 ± 0.056928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.205046 ± 0.043503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.792304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.219168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.185372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.198900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.974974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.974909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.585814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.220331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.227831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.665586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.192512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.215872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.739590</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.184377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.234454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.020827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.193811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.231487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.214469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.236663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.670599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.226710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.236712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891820</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.897323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.191801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.223183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.739972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.192557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.234380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.117615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.022175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.179389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.194035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.202809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.193098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.235124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778447</t>
+    <t xml:space="preserve">0.470103 ± 0.031386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922748 ± 0.003241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.579768 ± 0.035184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284221 ± 0.012684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805127 ± 0.030657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281133 ± 0.023931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330330 ± 0.023806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.169174 ± 0.024350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921596 ± 0.007799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.180147 ± 0.018586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.226620 ± 0.021723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790051 ± 0.021556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.208546 ± 0.041157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.238517 ± 0.045900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962029 ± 0.000904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982701 ± 0.000646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970579 ± 0.000807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518315 ± 0.009676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889111 ± 0.012770</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587155 ± 0.006891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890042 ± 0.002287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493727 ± 0.018957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927081 ± 0.006289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603955 ± 0.020926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298051 ± 0.017887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803863 ± 0.034669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296615 ± 0.026078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342626 ± 0.028628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750992</t>
   </si>
   <si>
     <t xml:space="preserve">COMPONENTES DEL PCA POR COLUMNAS</t>
@@ -4284,14 +3810,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>170280</xdr:rowOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>151200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>308160</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>104040</xdr:rowOff>
+      <xdr:colOff>307440</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>84240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4305,7 +3831,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="15723720" y="18970200"/>
-          <a:ext cx="5222520" cy="3890880"/>
+          <a:ext cx="5221800" cy="3890160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4321,14 +3847,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>88920</xdr:rowOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>69840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>308160</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>20880</xdr:rowOff>
+      <xdr:colOff>307440</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4342,7 +3868,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="15723720" y="23262480"/>
-          <a:ext cx="5222520" cy="3889440"/>
+          <a:ext cx="5221800" cy="3888720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4359,13 +3885,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>123</xdr:row>
-      <xdr:rowOff>7920</xdr:rowOff>
+      <xdr:rowOff>197280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>308160</xdr:colOff>
-      <xdr:row>141</xdr:row>
-      <xdr:rowOff>167400</xdr:rowOff>
+      <xdr:colOff>307440</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>150840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4379,7 +3905,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="15723720" y="27555480"/>
-          <a:ext cx="5222520" cy="3889440"/>
+          <a:ext cx="5221800" cy="3888720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4395,14 +3921,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>170280</xdr:rowOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>151200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>331920</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>102600</xdr:rowOff>
+      <xdr:colOff>331200</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>82800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4416,7 +3942,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="21906360" y="18970200"/>
-          <a:ext cx="5220000" cy="3889440"/>
+          <a:ext cx="5219280" cy="3888720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4432,14 +3958,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>88920</xdr:rowOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>69840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>331920</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>20880</xdr:rowOff>
+      <xdr:colOff>331200</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4453,7 +3979,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="21906360" y="23262480"/>
-          <a:ext cx="5220000" cy="3889440"/>
+          <a:ext cx="5219280" cy="3888720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4475,13 +4001,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>86</xdr:row>
-      <xdr:rowOff>141840</xdr:rowOff>
+      <xdr:rowOff>147960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>847080</xdr:colOff>
+      <xdr:colOff>846360</xdr:colOff>
       <xdr:row>104</xdr:row>
-      <xdr:rowOff>95760</xdr:rowOff>
+      <xdr:rowOff>101520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4495,7 +4021,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14133960" y="28371960"/>
-          <a:ext cx="5655240" cy="3892320"/>
+          <a:ext cx="5654520" cy="3891600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4512,13 +4038,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>107</xdr:row>
-      <xdr:rowOff>14400</xdr:rowOff>
+      <xdr:rowOff>20880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>404280</xdr:colOff>
+      <xdr:colOff>403560</xdr:colOff>
       <xdr:row>125</xdr:row>
-      <xdr:rowOff>157680</xdr:rowOff>
+      <xdr:rowOff>163440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4532,7 +4058,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14133960" y="32807880"/>
-          <a:ext cx="5212440" cy="3892320"/>
+          <a:ext cx="5211720" cy="3891600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4549,13 +4075,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>127</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>149760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>404280</xdr:colOff>
+      <xdr:colOff>403560</xdr:colOff>
       <xdr:row>146</xdr:row>
-      <xdr:rowOff>129240</xdr:rowOff>
+      <xdr:rowOff>135000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4569,7 +4095,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14133960" y="37102320"/>
-          <a:ext cx="5212440" cy="3892320"/>
+          <a:ext cx="5211720" cy="3891600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4586,13 +4112,13 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>86</xdr:row>
-      <xdr:rowOff>141840</xdr:rowOff>
+      <xdr:rowOff>147960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>335880</xdr:colOff>
+      <xdr:colOff>335160</xdr:colOff>
       <xdr:row>104</xdr:row>
-      <xdr:rowOff>95760</xdr:rowOff>
+      <xdr:rowOff>101520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4606,7 +4132,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="20526480" y="28371960"/>
-          <a:ext cx="5223960" cy="3892320"/>
+          <a:ext cx="5223240" cy="3891600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4623,13 +4149,13 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>107</xdr:row>
-      <xdr:rowOff>14400</xdr:rowOff>
+      <xdr:rowOff>20880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>335880</xdr:colOff>
+      <xdr:colOff>335160</xdr:colOff>
       <xdr:row>125</xdr:row>
-      <xdr:rowOff>157680</xdr:rowOff>
+      <xdr:rowOff>163440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4643,7 +4169,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="20526480" y="32807880"/>
-          <a:ext cx="5223960" cy="3892320"/>
+          <a:ext cx="5223240" cy="3891600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4665,13 +4191,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>1714680</xdr:colOff>
       <xdr:row>78</xdr:row>
-      <xdr:rowOff>237240</xdr:rowOff>
+      <xdr:rowOff>426600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>190440</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>86400</xdr:rowOff>
+      <xdr:colOff>189720</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>69840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4685,7 +4211,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1714680" y="21578400"/>
-          <a:ext cx="5475960" cy="3880800"/>
+          <a:ext cx="5475240" cy="3880080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4702,13 +4228,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>78</xdr:row>
-      <xdr:rowOff>173160</xdr:rowOff>
+      <xdr:rowOff>362520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>748080</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>22320</xdr:rowOff>
+      <xdr:colOff>747360</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>5760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4722,7 +4248,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8468280" y="21514320"/>
-          <a:ext cx="5170320" cy="3880800"/>
+          <a:ext cx="5169600" cy="3880080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4739,13 +4265,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>78</xdr:row>
-      <xdr:rowOff>173160</xdr:rowOff>
+      <xdr:rowOff>362520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>265320</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>22320</xdr:rowOff>
+      <xdr:colOff>264600</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>5760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4759,7 +4285,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14306400" y="21514320"/>
-          <a:ext cx="5235480" cy="3880800"/>
+          <a:ext cx="5234760" cy="3880080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4775,14 +4301,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1899360</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>173160</xdr:rowOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>157320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>375120</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>156960</xdr:rowOff>
+      <xdr:colOff>374400</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>140400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4796,7 +4322,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1899360" y="26161200"/>
-          <a:ext cx="5475960" cy="3880800"/>
+          <a:ext cx="5475240" cy="3880080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4812,14 +4338,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>173160</xdr:rowOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>157320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>748080</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>156960</xdr:rowOff>
+      <xdr:colOff>747360</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>140400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4833,7 +4359,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8468280" y="26161200"/>
-          <a:ext cx="5170320" cy="3880800"/>
+          <a:ext cx="5169600" cy="3880080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6691,7 +6217,7 @@
       <c r="K38" s="42"/>
       <c r="L38" s="35"/>
     </row>
-    <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
         <v>20</v>
       </c>
@@ -9968,33 +9494,15 @@
       <c r="B27" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="42" t="s">
-        <v>494</v>
-      </c>
-      <c r="D27" s="42" t="s">
-        <v>495</v>
-      </c>
-      <c r="E27" s="42" t="s">
-        <v>494</v>
-      </c>
-      <c r="F27" s="42" t="s">
-        <v>496</v>
-      </c>
-      <c r="G27" s="42" t="s">
-        <v>497</v>
-      </c>
-      <c r="H27" s="42" t="s">
-        <v>498</v>
-      </c>
-      <c r="I27" s="42" t="s">
-        <v>499</v>
-      </c>
-      <c r="J27" s="42" t="s">
-        <v>500</v>
-      </c>
-      <c r="K27" s="42" t="s">
-        <v>501</v>
-      </c>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="42"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
@@ -10033,33 +9541,15 @@
       <c r="B28" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="C28" s="42" t="s">
-        <v>502</v>
-      </c>
-      <c r="D28" s="42" t="s">
-        <v>503</v>
-      </c>
-      <c r="E28" s="42" t="s">
-        <v>502</v>
-      </c>
-      <c r="F28" s="42" t="s">
-        <v>504</v>
-      </c>
-      <c r="G28" s="42" t="s">
-        <v>505</v>
-      </c>
-      <c r="H28" s="42" t="s">
-        <v>506</v>
-      </c>
-      <c r="I28" s="42" t="s">
-        <v>507</v>
-      </c>
-      <c r="J28" s="42" t="s">
-        <v>508</v>
-      </c>
-      <c r="K28" s="42" t="s">
-        <v>501</v>
-      </c>
+      <c r="C28" s="42"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="42"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -10098,33 +9588,15 @@
       <c r="B29" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="C29" s="42" t="s">
-        <v>509</v>
-      </c>
-      <c r="D29" s="42" t="s">
-        <v>510</v>
-      </c>
-      <c r="E29" s="42" t="s">
-        <v>509</v>
-      </c>
-      <c r="F29" s="42" t="s">
-        <v>511</v>
-      </c>
-      <c r="G29" s="42" t="s">
-        <v>512</v>
-      </c>
-      <c r="H29" s="42" t="s">
-        <v>513</v>
-      </c>
-      <c r="I29" s="42" t="s">
-        <v>514</v>
-      </c>
-      <c r="J29" s="42" t="s">
-        <v>515</v>
-      </c>
-      <c r="K29" s="42" t="s">
-        <v>501</v>
-      </c>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="42"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -10164,28 +9636,28 @@
         <v>105</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>516</v>
+        <v>494</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>517</v>
+        <v>495</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>516</v>
+        <v>494</v>
       </c>
       <c r="F30" s="42" t="s">
-        <v>518</v>
+        <v>496</v>
       </c>
       <c r="G30" s="42" t="s">
-        <v>519</v>
+        <v>497</v>
       </c>
       <c r="H30" s="42" t="s">
-        <v>520</v>
+        <v>498</v>
       </c>
       <c r="I30" s="42" t="s">
-        <v>521</v>
+        <v>499</v>
       </c>
       <c r="J30" s="42" t="s">
-        <v>522</v>
+        <v>500</v>
       </c>
       <c r="K30" s="42" t="s">
         <v>501</v>
@@ -10228,33 +9700,15 @@
       <c r="B31" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="42" t="s">
-        <v>523</v>
-      </c>
-      <c r="D31" s="42" t="s">
-        <v>524</v>
-      </c>
-      <c r="E31" s="42" t="s">
-        <v>523</v>
-      </c>
-      <c r="F31" s="42" t="s">
-        <v>525</v>
-      </c>
-      <c r="G31" s="42" t="s">
-        <v>526</v>
-      </c>
-      <c r="H31" s="42" t="s">
-        <v>527</v>
-      </c>
-      <c r="I31" s="42" t="s">
-        <v>528</v>
-      </c>
-      <c r="J31" s="42" t="s">
-        <v>529</v>
-      </c>
-      <c r="K31" s="42" t="s">
-        <v>501</v>
-      </c>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
@@ -10293,33 +9747,15 @@
       <c r="B32" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="42" t="s">
-        <v>530</v>
-      </c>
-      <c r="D32" s="42" t="s">
-        <v>531</v>
-      </c>
-      <c r="E32" s="42" t="s">
-        <v>530</v>
-      </c>
-      <c r="F32" s="42" t="s">
-        <v>532</v>
-      </c>
-      <c r="G32" s="42" t="s">
-        <v>533</v>
-      </c>
-      <c r="H32" s="42" t="s">
-        <v>534</v>
-      </c>
-      <c r="I32" s="42" t="s">
-        <v>535</v>
-      </c>
-      <c r="J32" s="42" t="s">
-        <v>536</v>
-      </c>
-      <c r="K32" s="42" t="s">
-        <v>501</v>
-      </c>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -10359,28 +9795,28 @@
         <v>108</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>537</v>
+        <v>502</v>
       </c>
       <c r="D33" s="42" t="s">
-        <v>538</v>
+        <v>503</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>537</v>
+        <v>502</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>539</v>
+        <v>504</v>
       </c>
       <c r="G33" s="42" t="s">
-        <v>540</v>
+        <v>505</v>
       </c>
       <c r="H33" s="42" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="I33" s="42" t="s">
-        <v>542</v>
+        <v>507</v>
       </c>
       <c r="J33" s="42" t="s">
-        <v>543</v>
+        <v>508</v>
       </c>
       <c r="K33" s="42" t="s">
         <v>501</v>
@@ -10424,28 +9860,28 @@
         <v>109</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>544</v>
+        <v>509</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>545</v>
+        <v>510</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>544</v>
+        <v>509</v>
       </c>
       <c r="F34" s="42" t="s">
-        <v>546</v>
+        <v>511</v>
       </c>
       <c r="G34" s="42" t="s">
-        <v>547</v>
+        <v>512</v>
       </c>
       <c r="H34" s="42" t="s">
-        <v>548</v>
+        <v>513</v>
       </c>
       <c r="I34" s="42" t="s">
-        <v>549</v>
+        <v>514</v>
       </c>
       <c r="J34" s="42" t="s">
-        <v>550</v>
+        <v>515</v>
       </c>
       <c r="K34" s="42" t="s">
         <v>501</v>
@@ -10488,33 +9924,15 @@
       <c r="B35" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="42" t="s">
-        <v>551</v>
-      </c>
-      <c r="D35" s="42" t="s">
-        <v>552</v>
-      </c>
-      <c r="E35" s="42" t="s">
-        <v>551</v>
-      </c>
-      <c r="F35" s="42" t="s">
-        <v>553</v>
-      </c>
-      <c r="G35" s="42" t="s">
-        <v>554</v>
-      </c>
-      <c r="H35" s="42" t="s">
-        <v>555</v>
-      </c>
-      <c r="I35" s="42" t="s">
-        <v>556</v>
-      </c>
-      <c r="J35" s="42" t="s">
-        <v>557</v>
-      </c>
-      <c r="K35" s="42" t="s">
-        <v>501</v>
-      </c>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="42"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -10554,28 +9972,28 @@
         <v>111</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>558</v>
+        <v>516</v>
       </c>
       <c r="D36" s="42" t="s">
-        <v>559</v>
+        <v>517</v>
       </c>
       <c r="E36" s="42" t="s">
-        <v>558</v>
+        <v>516</v>
       </c>
       <c r="F36" s="42" t="s">
-        <v>560</v>
+        <v>518</v>
       </c>
       <c r="G36" s="42" t="s">
-        <v>561</v>
+        <v>519</v>
       </c>
       <c r="H36" s="42" t="s">
-        <v>562</v>
+        <v>520</v>
       </c>
       <c r="I36" s="42" t="s">
-        <v>563</v>
+        <v>521</v>
       </c>
       <c r="J36" s="42" t="s">
-        <v>564</v>
+        <v>522</v>
       </c>
       <c r="K36" s="42" t="s">
         <v>501</v>
@@ -10618,33 +10036,15 @@
       <c r="B37" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="C37" s="42" t="s">
-        <v>565</v>
-      </c>
-      <c r="D37" s="42" t="s">
-        <v>566</v>
-      </c>
-      <c r="E37" s="42" t="s">
-        <v>565</v>
-      </c>
-      <c r="F37" s="42" t="s">
-        <v>567</v>
-      </c>
-      <c r="G37" s="42" t="s">
-        <v>568</v>
-      </c>
-      <c r="H37" s="42" t="s">
-        <v>569</v>
-      </c>
-      <c r="I37" s="42" t="s">
-        <v>570</v>
-      </c>
-      <c r="J37" s="42" t="s">
-        <v>571</v>
-      </c>
-      <c r="K37" s="42" t="s">
-        <v>501</v>
-      </c>
+      <c r="C37" s="42"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="42"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
@@ -10683,33 +10083,15 @@
       <c r="B38" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="42" t="s">
-        <v>572</v>
-      </c>
-      <c r="D38" s="42" t="s">
-        <v>573</v>
-      </c>
-      <c r="E38" s="42" t="s">
-        <v>572</v>
-      </c>
-      <c r="F38" s="42" t="s">
-        <v>574</v>
-      </c>
-      <c r="G38" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="H38" s="42" t="s">
-        <v>576</v>
-      </c>
-      <c r="I38" s="42" t="s">
-        <v>577</v>
-      </c>
-      <c r="J38" s="42" t="s">
-        <v>578</v>
-      </c>
-      <c r="K38" s="42" t="s">
-        <v>501</v>
-      </c>
+      <c r="C38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="42"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
@@ -10749,28 +10131,28 @@
         <v>114</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>579</v>
+        <v>523</v>
       </c>
       <c r="D39" s="42" t="s">
-        <v>580</v>
+        <v>524</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>579</v>
+        <v>523</v>
       </c>
       <c r="F39" s="42" t="s">
-        <v>581</v>
+        <v>525</v>
       </c>
       <c r="G39" s="42" t="s">
-        <v>582</v>
+        <v>526</v>
       </c>
       <c r="H39" s="42" t="s">
-        <v>583</v>
+        <v>527</v>
       </c>
       <c r="I39" s="42" t="s">
-        <v>584</v>
+        <v>528</v>
       </c>
       <c r="J39" s="42" t="s">
-        <v>585</v>
+        <v>529</v>
       </c>
       <c r="K39" s="42" t="s">
         <v>501</v>
@@ -10813,33 +10195,15 @@
       <c r="B40" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="C40" s="42" t="s">
-        <v>586</v>
-      </c>
-      <c r="D40" s="42" t="s">
-        <v>587</v>
-      </c>
-      <c r="E40" s="42" t="s">
-        <v>586</v>
-      </c>
-      <c r="F40" s="42" t="s">
-        <v>588</v>
-      </c>
-      <c r="G40" s="42" t="s">
-        <v>589</v>
-      </c>
-      <c r="H40" s="42" t="s">
-        <v>590</v>
-      </c>
-      <c r="I40" s="42" t="s">
-        <v>591</v>
-      </c>
-      <c r="J40" s="42" t="s">
-        <v>592</v>
-      </c>
-      <c r="K40" s="42" t="s">
-        <v>501</v>
-      </c>
+      <c r="C40" s="42"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="42"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
@@ -10878,33 +10242,15 @@
       <c r="B41" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="C41" s="42" t="s">
-        <v>593</v>
-      </c>
-      <c r="D41" s="42" t="s">
-        <v>594</v>
-      </c>
-      <c r="E41" s="42" t="s">
-        <v>593</v>
-      </c>
-      <c r="F41" s="42" t="s">
-        <v>595</v>
-      </c>
-      <c r="G41" s="42" t="s">
-        <v>596</v>
-      </c>
-      <c r="H41" s="42" t="s">
-        <v>597</v>
-      </c>
-      <c r="I41" s="42" t="s">
-        <v>598</v>
-      </c>
-      <c r="J41" s="42" t="s">
-        <v>599</v>
-      </c>
-      <c r="K41" s="42" t="s">
-        <v>501</v>
-      </c>
+      <c r="C41" s="42"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="42"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
@@ -11077,7 +10423,7 @@
       <c r="I50" s="57"/>
       <c r="J50" s="58"/>
     </row>
-    <row r="59" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="54" t="s">
         <v>91</v>
       </c>
@@ -11119,33 +10465,8 @@
       <c r="B60" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C60" s="42" t="s">
-        <v>600</v>
-      </c>
-      <c r="D60" s="42" t="s">
-        <v>601</v>
-      </c>
-      <c r="E60" s="42" t="s">
-        <v>600</v>
-      </c>
-      <c r="F60" s="42" t="s">
-        <v>602</v>
-      </c>
-      <c r="G60" s="42" t="s">
-        <v>603</v>
-      </c>
-      <c r="H60" s="42" t="s">
-        <v>604</v>
-      </c>
-      <c r="I60" s="42" t="s">
-        <v>605</v>
-      </c>
-      <c r="J60" s="42" t="s">
-        <v>606</v>
-      </c>
-      <c r="K60" s="42" t="s">
-        <v>607</v>
-      </c>
+      <c r="J60" s="42"/>
+      <c r="K60" s="42"/>
     </row>
     <row r="61" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="56" t="n">
@@ -11154,33 +10475,8 @@
       <c r="B61" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="C61" s="42" t="s">
-        <v>608</v>
-      </c>
-      <c r="D61" s="42" t="s">
-        <v>609</v>
-      </c>
-      <c r="E61" s="42" t="s">
-        <v>608</v>
-      </c>
-      <c r="F61" s="42" t="s">
-        <v>610</v>
-      </c>
-      <c r="G61" s="42" t="s">
-        <v>611</v>
-      </c>
-      <c r="H61" s="42" t="s">
-        <v>612</v>
-      </c>
-      <c r="I61" s="42" t="s">
-        <v>613</v>
-      </c>
-      <c r="J61" s="42" t="s">
-        <v>614</v>
-      </c>
-      <c r="K61" s="42" t="s">
-        <v>615</v>
-      </c>
+      <c r="J61" s="42"/>
+      <c r="K61" s="42"/>
     </row>
     <row r="62" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="56" t="n">
@@ -11189,33 +10485,8 @@
       <c r="B62" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="C62" s="42" t="s">
-        <v>616</v>
-      </c>
-      <c r="D62" s="42" t="s">
-        <v>617</v>
-      </c>
-      <c r="E62" s="42" t="s">
-        <v>616</v>
-      </c>
-      <c r="F62" s="42" t="s">
-        <v>618</v>
-      </c>
-      <c r="G62" s="42" t="s">
-        <v>619</v>
-      </c>
-      <c r="H62" s="42" t="s">
-        <v>620</v>
-      </c>
-      <c r="I62" s="42" t="s">
-        <v>621</v>
-      </c>
-      <c r="J62" s="42" t="s">
-        <v>622</v>
-      </c>
-      <c r="K62" s="42" t="s">
-        <v>623</v>
-      </c>
+      <c r="J62" s="42"/>
+      <c r="K62" s="42"/>
     </row>
     <row r="63" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="56" t="n">
@@ -11225,31 +10496,31 @@
         <v>105</v>
       </c>
       <c r="C63" s="42" t="s">
-        <v>624</v>
+        <v>530</v>
       </c>
       <c r="D63" s="42" t="s">
-        <v>625</v>
+        <v>531</v>
       </c>
       <c r="E63" s="42" t="s">
-        <v>624</v>
+        <v>530</v>
       </c>
       <c r="F63" s="42" t="s">
-        <v>626</v>
+        <v>532</v>
       </c>
       <c r="G63" s="42" t="s">
-        <v>627</v>
+        <v>533</v>
       </c>
       <c r="H63" s="42" t="s">
-        <v>628</v>
+        <v>534</v>
       </c>
       <c r="I63" s="42" t="s">
-        <v>629</v>
+        <v>535</v>
       </c>
       <c r="J63" s="42" t="s">
-        <v>630</v>
+        <v>536</v>
       </c>
       <c r="K63" s="42" t="s">
-        <v>631</v>
+        <v>537</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11259,33 +10530,8 @@
       <c r="B64" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="C64" s="42" t="s">
-        <v>632</v>
-      </c>
-      <c r="D64" s="42" t="s">
-        <v>633</v>
-      </c>
-      <c r="E64" s="42" t="s">
-        <v>632</v>
-      </c>
-      <c r="F64" s="42" t="s">
-        <v>634</v>
-      </c>
-      <c r="G64" s="42" t="s">
-        <v>635</v>
-      </c>
-      <c r="H64" s="42" t="s">
-        <v>636</v>
-      </c>
-      <c r="I64" s="42" t="s">
-        <v>637</v>
-      </c>
-      <c r="J64" s="42" t="s">
-        <v>638</v>
-      </c>
-      <c r="K64" s="42" t="s">
-        <v>639</v>
-      </c>
+      <c r="J64" s="42"/>
+      <c r="K64" s="42"/>
     </row>
     <row r="65" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="56" t="n">
@@ -11294,33 +10540,8 @@
       <c r="B65" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="C65" s="42" t="s">
-        <v>640</v>
-      </c>
-      <c r="D65" s="42" t="s">
-        <v>641</v>
-      </c>
-      <c r="E65" s="42" t="s">
-        <v>640</v>
-      </c>
-      <c r="F65" s="42" t="s">
-        <v>642</v>
-      </c>
-      <c r="G65" s="42" t="s">
-        <v>643</v>
-      </c>
-      <c r="H65" s="42" t="s">
-        <v>644</v>
-      </c>
-      <c r="I65" s="42" t="s">
-        <v>645</v>
-      </c>
-      <c r="J65" s="42" t="s">
-        <v>646</v>
-      </c>
-      <c r="K65" s="42" t="s">
-        <v>647</v>
-      </c>
+      <c r="J65" s="42"/>
+      <c r="K65" s="42"/>
     </row>
     <row r="66" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="56" t="n">
@@ -11330,31 +10551,31 @@
         <v>108</v>
       </c>
       <c r="C66" s="42" t="s">
-        <v>648</v>
+        <v>538</v>
       </c>
       <c r="D66" s="42" t="s">
-        <v>649</v>
+        <v>539</v>
       </c>
       <c r="E66" s="42" t="s">
-        <v>648</v>
+        <v>538</v>
       </c>
       <c r="F66" s="42" t="s">
-        <v>650</v>
+        <v>540</v>
       </c>
       <c r="G66" s="42" t="s">
-        <v>651</v>
+        <v>541</v>
       </c>
       <c r="H66" s="42" t="s">
-        <v>652</v>
+        <v>542</v>
       </c>
       <c r="I66" s="42" t="s">
-        <v>653</v>
+        <v>543</v>
       </c>
       <c r="J66" s="42" t="s">
-        <v>654</v>
+        <v>544</v>
       </c>
       <c r="K66" s="42" t="s">
-        <v>655</v>
+        <v>545</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11364,33 +10585,8 @@
       <c r="B67" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="C67" s="42" t="s">
-        <v>656</v>
-      </c>
-      <c r="D67" s="42" t="s">
-        <v>657</v>
-      </c>
-      <c r="E67" s="42" t="s">
-        <v>656</v>
-      </c>
-      <c r="F67" s="42" t="s">
-        <v>658</v>
-      </c>
-      <c r="G67" s="42" t="s">
-        <v>659</v>
-      </c>
-      <c r="H67" s="42" t="s">
-        <v>660</v>
-      </c>
-      <c r="I67" s="42" t="s">
-        <v>661</v>
-      </c>
-      <c r="J67" s="42" t="s">
-        <v>662</v>
-      </c>
-      <c r="K67" s="42" t="s">
-        <v>663</v>
-      </c>
+      <c r="J67" s="42"/>
+      <c r="K67" s="42"/>
     </row>
     <row r="68" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="n">
@@ -11399,33 +10595,8 @@
       <c r="B68" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="C68" s="42" t="s">
-        <v>664</v>
-      </c>
-      <c r="D68" s="42" t="s">
-        <v>665</v>
-      </c>
-      <c r="E68" s="42" t="s">
-        <v>664</v>
-      </c>
-      <c r="F68" s="42" t="s">
-        <v>666</v>
-      </c>
-      <c r="G68" s="42" t="s">
-        <v>667</v>
-      </c>
-      <c r="H68" s="42" t="s">
-        <v>668</v>
-      </c>
-      <c r="I68" s="42" t="s">
-        <v>669</v>
-      </c>
-      <c r="J68" s="42" t="s">
-        <v>670</v>
-      </c>
-      <c r="K68" s="42" t="s">
-        <v>671</v>
-      </c>
+      <c r="J68" s="42"/>
+      <c r="K68" s="42"/>
     </row>
     <row r="69" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="56" t="n">
@@ -11435,31 +10606,31 @@
         <v>111</v>
       </c>
       <c r="C69" s="42" t="s">
-        <v>672</v>
+        <v>546</v>
       </c>
       <c r="D69" s="42" t="s">
-        <v>673</v>
+        <v>547</v>
       </c>
       <c r="E69" s="42" t="s">
-        <v>672</v>
+        <v>546</v>
       </c>
       <c r="F69" s="42" t="s">
-        <v>674</v>
+        <v>548</v>
       </c>
       <c r="G69" s="42" t="s">
-        <v>675</v>
+        <v>549</v>
       </c>
       <c r="H69" s="42" t="s">
-        <v>676</v>
+        <v>550</v>
       </c>
       <c r="I69" s="42" t="s">
-        <v>677</v>
+        <v>551</v>
       </c>
       <c r="J69" s="42" t="s">
-        <v>678</v>
+        <v>552</v>
       </c>
       <c r="K69" s="42" t="s">
-        <v>679</v>
+        <v>553</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11469,33 +10640,8 @@
       <c r="B70" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="C70" s="42" t="s">
-        <v>680</v>
-      </c>
-      <c r="D70" s="42" t="s">
-        <v>681</v>
-      </c>
-      <c r="E70" s="42" t="s">
-        <v>680</v>
-      </c>
-      <c r="F70" s="42" t="s">
-        <v>682</v>
-      </c>
-      <c r="G70" s="42" t="s">
-        <v>683</v>
-      </c>
-      <c r="H70" s="42" t="s">
-        <v>684</v>
-      </c>
-      <c r="I70" s="42" t="s">
-        <v>685</v>
-      </c>
-      <c r="J70" s="42" t="s">
-        <v>686</v>
-      </c>
-      <c r="K70" s="42" t="s">
-        <v>687</v>
-      </c>
+      <c r="J70" s="42"/>
+      <c r="K70" s="42"/>
     </row>
     <row r="71" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="56" t="n">
@@ -11504,33 +10650,8 @@
       <c r="B71" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="C71" s="42" t="s">
-        <v>688</v>
-      </c>
-      <c r="D71" s="42" t="s">
-        <v>689</v>
-      </c>
-      <c r="E71" s="42" t="s">
-        <v>688</v>
-      </c>
-      <c r="F71" s="42" t="s">
-        <v>690</v>
-      </c>
-      <c r="G71" s="42" t="s">
-        <v>691</v>
-      </c>
-      <c r="H71" s="42" t="s">
-        <v>692</v>
-      </c>
-      <c r="I71" s="42" t="s">
-        <v>693</v>
-      </c>
-      <c r="J71" s="42" t="s">
-        <v>694</v>
-      </c>
-      <c r="K71" s="42" t="s">
-        <v>695</v>
-      </c>
+      <c r="J71" s="42"/>
+      <c r="K71" s="42"/>
     </row>
     <row r="72" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
@@ -11540,31 +10661,31 @@
         <v>114</v>
       </c>
       <c r="C72" s="42" t="s">
-        <v>696</v>
+        <v>554</v>
       </c>
       <c r="D72" s="42" t="s">
-        <v>697</v>
+        <v>555</v>
       </c>
       <c r="E72" s="42" t="s">
-        <v>696</v>
+        <v>554</v>
       </c>
       <c r="F72" s="42" t="s">
-        <v>698</v>
+        <v>556</v>
       </c>
       <c r="G72" s="42" t="s">
-        <v>699</v>
+        <v>557</v>
       </c>
       <c r="H72" s="42" t="s">
-        <v>700</v>
+        <v>558</v>
       </c>
       <c r="I72" s="42" t="s">
-        <v>701</v>
+        <v>559</v>
       </c>
       <c r="J72" s="42" t="s">
-        <v>702</v>
+        <v>560</v>
       </c>
       <c r="K72" s="42" t="s">
-        <v>703</v>
+        <v>561</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11574,33 +10695,8 @@
       <c r="B73" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="C73" s="42" t="s">
-        <v>704</v>
-      </c>
-      <c r="D73" s="42" t="s">
-        <v>705</v>
-      </c>
-      <c r="E73" s="42" t="s">
-        <v>704</v>
-      </c>
-      <c r="F73" s="42" t="s">
-        <v>706</v>
-      </c>
-      <c r="G73" s="42" t="s">
-        <v>707</v>
-      </c>
-      <c r="H73" s="42" t="s">
-        <v>708</v>
-      </c>
-      <c r="I73" s="42" t="s">
-        <v>709</v>
-      </c>
-      <c r="J73" s="42" t="s">
-        <v>710</v>
-      </c>
-      <c r="K73" s="42" t="s">
-        <v>711</v>
-      </c>
+      <c r="J73" s="42"/>
+      <c r="K73" s="42"/>
     </row>
     <row r="74" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="56" t="n">
@@ -11609,37 +10705,12 @@
       <c r="B74" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="C74" s="42" t="s">
-        <v>712</v>
-      </c>
-      <c r="D74" s="42" t="s">
-        <v>713</v>
-      </c>
-      <c r="E74" s="42" t="s">
-        <v>712</v>
-      </c>
-      <c r="F74" s="42" t="s">
-        <v>714</v>
-      </c>
-      <c r="G74" s="42" t="s">
-        <v>715</v>
-      </c>
-      <c r="H74" s="42" t="s">
-        <v>716</v>
-      </c>
-      <c r="I74" s="42" t="s">
-        <v>717</v>
-      </c>
-      <c r="J74" s="42" t="s">
-        <v>718</v>
-      </c>
-      <c r="K74" s="42" t="s">
-        <v>719</v>
-      </c>
+      <c r="J74" s="42"/>
+      <c r="K74" s="42"/>
     </row>
     <row r="82" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="35" t="s">
-        <v>720</v>
+        <v>562</v>
       </c>
       <c r="B82" s="35"/>
       <c r="C82" s="35"/>
@@ -11668,22 +10739,22 @@
     </row>
     <row r="84" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="60" t="s">
-        <v>721</v>
+        <v>563</v>
       </c>
       <c r="B84" s="42" t="s">
-        <v>722</v>
+        <v>564</v>
       </c>
       <c r="C84" s="42" t="s">
-        <v>723</v>
+        <v>565</v>
       </c>
       <c r="D84" s="42" t="s">
-        <v>724</v>
+        <v>566</v>
       </c>
       <c r="E84" s="42" t="s">
-        <v>725</v>
+        <v>567</v>
       </c>
       <c r="F84" s="42" t="s">
-        <v>726</v>
+        <v>568</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11691,199 +10762,199 @@
         <v>134</v>
       </c>
       <c r="B85" s="42" t="s">
-        <v>727</v>
+        <v>569</v>
       </c>
       <c r="C85" s="42" t="s">
-        <v>728</v>
+        <v>570</v>
       </c>
       <c r="D85" s="42" t="s">
-        <v>729</v>
+        <v>571</v>
       </c>
       <c r="E85" s="42" t="s">
-        <v>730</v>
+        <v>572</v>
       </c>
       <c r="F85" s="42" t="s">
-        <v>731</v>
+        <v>573</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="60" t="s">
-        <v>732</v>
+        <v>574</v>
       </c>
       <c r="B86" s="42" t="s">
-        <v>733</v>
+        <v>575</v>
       </c>
       <c r="C86" s="42" t="s">
-        <v>734</v>
+        <v>576</v>
       </c>
       <c r="D86" s="42" t="s">
-        <v>735</v>
+        <v>577</v>
       </c>
       <c r="E86" s="42" t="s">
-        <v>736</v>
+        <v>578</v>
       </c>
       <c r="F86" s="42" t="s">
-        <v>737</v>
+        <v>579</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="60" t="s">
-        <v>738</v>
+        <v>580</v>
       </c>
       <c r="B87" s="42" t="s">
-        <v>739</v>
+        <v>581</v>
       </c>
       <c r="C87" s="42" t="s">
-        <v>740</v>
+        <v>582</v>
       </c>
       <c r="D87" s="42" t="s">
-        <v>741</v>
+        <v>583</v>
       </c>
       <c r="E87" s="42" t="s">
-        <v>742</v>
+        <v>584</v>
       </c>
       <c r="F87" s="42" t="s">
-        <v>743</v>
+        <v>585</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="60" t="s">
-        <v>744</v>
+        <v>586</v>
       </c>
       <c r="B88" s="42" t="s">
-        <v>745</v>
+        <v>587</v>
       </c>
       <c r="C88" s="42" t="s">
-        <v>746</v>
+        <v>588</v>
       </c>
       <c r="D88" s="42" t="s">
-        <v>747</v>
+        <v>589</v>
       </c>
       <c r="E88" s="42" t="s">
-        <v>748</v>
+        <v>590</v>
       </c>
       <c r="F88" s="42" t="s">
-        <v>749</v>
+        <v>591</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="60" t="s">
-        <v>750</v>
+        <v>592</v>
       </c>
       <c r="B89" s="42" t="s">
-        <v>751</v>
+        <v>593</v>
       </c>
       <c r="C89" s="42" t="s">
-        <v>752</v>
+        <v>594</v>
       </c>
       <c r="D89" s="42" t="s">
-        <v>753</v>
+        <v>595</v>
       </c>
       <c r="E89" s="42" t="s">
-        <v>754</v>
+        <v>596</v>
       </c>
       <c r="F89" s="42" t="s">
-        <v>755</v>
+        <v>597</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="60" t="s">
-        <v>756</v>
+        <v>598</v>
       </c>
       <c r="B90" s="42" t="s">
-        <v>757</v>
+        <v>599</v>
       </c>
       <c r="C90" s="42" t="s">
-        <v>758</v>
+        <v>600</v>
       </c>
       <c r="D90" s="42" t="s">
-        <v>759</v>
+        <v>601</v>
       </c>
       <c r="E90" s="42" t="s">
-        <v>760</v>
+        <v>602</v>
       </c>
       <c r="F90" s="42" t="s">
-        <v>761</v>
+        <v>603</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="60" t="s">
-        <v>762</v>
+        <v>604</v>
       </c>
       <c r="B91" s="42" t="s">
-        <v>763</v>
+        <v>605</v>
       </c>
       <c r="C91" s="42" t="s">
-        <v>764</v>
+        <v>606</v>
       </c>
       <c r="D91" s="42" t="s">
-        <v>765</v>
+        <v>607</v>
       </c>
       <c r="E91" s="42" t="s">
-        <v>766</v>
+        <v>608</v>
       </c>
       <c r="F91" s="42" t="s">
-        <v>767</v>
+        <v>609</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="60" t="s">
-        <v>768</v>
+        <v>610</v>
       </c>
       <c r="B92" s="42" t="s">
-        <v>769</v>
+        <v>611</v>
       </c>
       <c r="C92" s="42" t="s">
-        <v>770</v>
+        <v>612</v>
       </c>
       <c r="D92" s="42" t="s">
-        <v>771</v>
+        <v>613</v>
       </c>
       <c r="E92" s="42" t="s">
-        <v>772</v>
+        <v>614</v>
       </c>
       <c r="F92" s="42" t="s">
-        <v>773</v>
+        <v>615</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="60" t="s">
-        <v>774</v>
+        <v>616</v>
       </c>
       <c r="B93" s="42" t="s">
-        <v>775</v>
+        <v>617</v>
       </c>
       <c r="C93" s="42" t="s">
-        <v>776</v>
+        <v>618</v>
       </c>
       <c r="D93" s="42" t="s">
-        <v>777</v>
+        <v>619</v>
       </c>
       <c r="E93" s="42" t="s">
-        <v>778</v>
+        <v>620</v>
       </c>
       <c r="F93" s="42" t="s">
-        <v>779</v>
+        <v>621</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="60" t="s">
-        <v>780</v>
+        <v>622</v>
       </c>
       <c r="B94" s="42" t="s">
-        <v>781</v>
+        <v>623</v>
       </c>
       <c r="C94" s="42" t="s">
-        <v>782</v>
+        <v>624</v>
       </c>
       <c r="D94" s="42" t="s">
-        <v>783</v>
+        <v>625</v>
       </c>
       <c r="E94" s="42" t="s">
-        <v>784</v>
+        <v>626</v>
       </c>
       <c r="F94" s="42" t="s">
-        <v>785</v>
+        <v>627</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11891,19 +10962,19 @@
         <v>224</v>
       </c>
       <c r="B95" s="42" t="s">
-        <v>786</v>
+        <v>628</v>
       </c>
       <c r="C95" s="42" t="s">
-        <v>787</v>
+        <v>629</v>
       </c>
       <c r="D95" s="42" t="s">
-        <v>788</v>
+        <v>630</v>
       </c>
       <c r="E95" s="42" t="s">
-        <v>789</v>
+        <v>631</v>
       </c>
       <c r="F95" s="42" t="s">
-        <v>790</v>
+        <v>632</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11911,19 +10982,19 @@
         <v>230</v>
       </c>
       <c r="B96" s="42" t="s">
-        <v>791</v>
+        <v>633</v>
       </c>
       <c r="C96" s="42" t="s">
-        <v>792</v>
+        <v>634</v>
       </c>
       <c r="D96" s="42" t="s">
-        <v>793</v>
+        <v>635</v>
       </c>
       <c r="E96" s="42" t="s">
-        <v>794</v>
+        <v>636</v>
       </c>
       <c r="F96" s="42" t="s">
-        <v>795</v>
+        <v>637</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11931,19 +11002,19 @@
         <v>236</v>
       </c>
       <c r="B97" s="42" t="s">
-        <v>796</v>
+        <v>638</v>
       </c>
       <c r="C97" s="42" t="s">
-        <v>797</v>
+        <v>639</v>
       </c>
       <c r="D97" s="42" t="s">
-        <v>798</v>
+        <v>640</v>
       </c>
       <c r="E97" s="42" t="s">
-        <v>799</v>
+        <v>641</v>
       </c>
       <c r="F97" s="42" t="s">
-        <v>800</v>
+        <v>642</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11951,19 +11022,19 @@
         <v>242</v>
       </c>
       <c r="B98" s="42" t="s">
-        <v>801</v>
+        <v>643</v>
       </c>
       <c r="C98" s="42" t="s">
-        <v>802</v>
+        <v>644</v>
       </c>
       <c r="D98" s="42" t="s">
-        <v>803</v>
+        <v>645</v>
       </c>
       <c r="E98" s="42" t="s">
-        <v>804</v>
+        <v>646</v>
       </c>
       <c r="F98" s="42" t="s">
-        <v>805</v>
+        <v>647</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11971,19 +11042,19 @@
         <v>254</v>
       </c>
       <c r="B99" s="42" t="s">
-        <v>806</v>
+        <v>648</v>
       </c>
       <c r="C99" s="42" t="s">
-        <v>807</v>
+        <v>649</v>
       </c>
       <c r="D99" s="42" t="s">
-        <v>808</v>
+        <v>650</v>
       </c>
       <c r="E99" s="42" t="s">
-        <v>809</v>
+        <v>651</v>
       </c>
       <c r="F99" s="42" t="s">
-        <v>810</v>
+        <v>652</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11991,19 +11062,19 @@
         <v>260</v>
       </c>
       <c r="B100" s="42" t="s">
-        <v>811</v>
+        <v>653</v>
       </c>
       <c r="C100" s="42" t="s">
-        <v>812</v>
+        <v>654</v>
       </c>
       <c r="D100" s="42" t="s">
-        <v>813</v>
+        <v>655</v>
       </c>
       <c r="E100" s="42" t="s">
-        <v>814</v>
+        <v>656</v>
       </c>
       <c r="F100" s="42" t="s">
-        <v>815</v>
+        <v>657</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12011,39 +11082,39 @@
         <v>272</v>
       </c>
       <c r="B101" s="42" t="s">
-        <v>816</v>
+        <v>658</v>
       </c>
       <c r="C101" s="42" t="s">
-        <v>817</v>
+        <v>659</v>
       </c>
       <c r="D101" s="42" t="s">
-        <v>818</v>
+        <v>660</v>
       </c>
       <c r="E101" s="42" t="s">
-        <v>819</v>
+        <v>661</v>
       </c>
       <c r="F101" s="42" t="s">
-        <v>820</v>
+        <v>662</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="60" t="s">
-        <v>821</v>
+        <v>663</v>
       </c>
       <c r="B102" s="42" t="s">
-        <v>822</v>
+        <v>664</v>
       </c>
       <c r="C102" s="42" t="s">
-        <v>823</v>
+        <v>665</v>
       </c>
       <c r="D102" s="42" t="s">
-        <v>824</v>
+        <v>666</v>
       </c>
       <c r="E102" s="42" t="s">
-        <v>825</v>
+        <v>667</v>
       </c>
       <c r="F102" s="42" t="s">
-        <v>826</v>
+        <v>668</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12051,19 +11122,19 @@
         <v>284</v>
       </c>
       <c r="B103" s="42" t="s">
-        <v>827</v>
+        <v>669</v>
       </c>
       <c r="C103" s="42" t="s">
-        <v>828</v>
+        <v>670</v>
       </c>
       <c r="D103" s="42" t="s">
-        <v>829</v>
+        <v>671</v>
       </c>
       <c r="E103" s="42" t="s">
-        <v>830</v>
+        <v>672</v>
       </c>
       <c r="F103" s="42" t="s">
-        <v>831</v>
+        <v>673</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12071,19 +11142,19 @@
         <v>290</v>
       </c>
       <c r="B104" s="42" t="s">
-        <v>832</v>
+        <v>674</v>
       </c>
       <c r="C104" s="42" t="s">
-        <v>833</v>
+        <v>675</v>
       </c>
       <c r="D104" s="42" t="s">
-        <v>834</v>
+        <v>676</v>
       </c>
       <c r="E104" s="42" t="s">
-        <v>835</v>
+        <v>677</v>
       </c>
       <c r="F104" s="42" t="s">
-        <v>836</v>
+        <v>678</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12091,19 +11162,19 @@
         <v>296</v>
       </c>
       <c r="B105" s="42" t="s">
-        <v>837</v>
+        <v>679</v>
       </c>
       <c r="C105" s="42" t="s">
-        <v>838</v>
+        <v>680</v>
       </c>
       <c r="D105" s="42" t="s">
-        <v>839</v>
+        <v>681</v>
       </c>
       <c r="E105" s="42" t="s">
-        <v>840</v>
+        <v>682</v>
       </c>
       <c r="F105" s="42" t="s">
-        <v>841</v>
+        <v>683</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12111,19 +11182,19 @@
         <v>302</v>
       </c>
       <c r="B106" s="42" t="s">
-        <v>842</v>
+        <v>684</v>
       </c>
       <c r="C106" s="42" t="s">
-        <v>843</v>
+        <v>685</v>
       </c>
       <c r="D106" s="42" t="s">
-        <v>844</v>
+        <v>686</v>
       </c>
       <c r="E106" s="42" t="s">
-        <v>845</v>
+        <v>687</v>
       </c>
       <c r="F106" s="42" t="s">
-        <v>846</v>
+        <v>688</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12131,379 +11202,379 @@
         <v>308</v>
       </c>
       <c r="B107" s="42" t="s">
-        <v>847</v>
+        <v>689</v>
       </c>
       <c r="C107" s="42" t="s">
-        <v>848</v>
+        <v>690</v>
       </c>
       <c r="D107" s="42" t="s">
-        <v>849</v>
+        <v>691</v>
       </c>
       <c r="E107" s="42" t="s">
-        <v>850</v>
+        <v>692</v>
       </c>
       <c r="F107" s="42" t="s">
-        <v>851</v>
+        <v>693</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="60" t="s">
-        <v>852</v>
+        <v>694</v>
       </c>
       <c r="B108" s="42" t="s">
-        <v>853</v>
+        <v>695</v>
       </c>
       <c r="C108" s="42" t="s">
-        <v>854</v>
+        <v>696</v>
       </c>
       <c r="D108" s="42" t="s">
-        <v>855</v>
+        <v>697</v>
       </c>
       <c r="E108" s="42" t="s">
-        <v>856</v>
+        <v>698</v>
       </c>
       <c r="F108" s="42" t="s">
-        <v>857</v>
+        <v>699</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="60" t="s">
-        <v>858</v>
+        <v>700</v>
       </c>
       <c r="B109" s="42" t="s">
-        <v>859</v>
+        <v>701</v>
       </c>
       <c r="C109" s="42" t="s">
-        <v>860</v>
+        <v>702</v>
       </c>
       <c r="D109" s="42" t="s">
-        <v>861</v>
+        <v>703</v>
       </c>
       <c r="E109" s="42" t="s">
-        <v>862</v>
+        <v>704</v>
       </c>
       <c r="F109" s="42" t="s">
-        <v>863</v>
+        <v>705</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="60" t="s">
-        <v>864</v>
+        <v>706</v>
       </c>
       <c r="B110" s="42" t="s">
-        <v>865</v>
+        <v>707</v>
       </c>
       <c r="C110" s="42" t="s">
-        <v>866</v>
+        <v>708</v>
       </c>
       <c r="D110" s="42" t="s">
-        <v>867</v>
+        <v>709</v>
       </c>
       <c r="E110" s="42" t="s">
-        <v>868</v>
+        <v>710</v>
       </c>
       <c r="F110" s="42" t="s">
-        <v>869</v>
+        <v>711</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="60" t="s">
-        <v>870</v>
+        <v>712</v>
       </c>
       <c r="B111" s="42" t="s">
-        <v>871</v>
+        <v>713</v>
       </c>
       <c r="C111" s="42" t="s">
-        <v>872</v>
+        <v>714</v>
       </c>
       <c r="D111" s="42" t="s">
-        <v>873</v>
+        <v>715</v>
       </c>
       <c r="E111" s="42" t="s">
-        <v>874</v>
+        <v>716</v>
       </c>
       <c r="F111" s="42" t="s">
-        <v>875</v>
+        <v>717</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="60" t="s">
-        <v>876</v>
+        <v>718</v>
       </c>
       <c r="B112" s="42" t="s">
-        <v>877</v>
+        <v>719</v>
       </c>
       <c r="C112" s="42" t="s">
-        <v>878</v>
+        <v>720</v>
       </c>
       <c r="D112" s="42" t="s">
-        <v>879</v>
+        <v>721</v>
       </c>
       <c r="E112" s="42" t="s">
-        <v>880</v>
+        <v>722</v>
       </c>
       <c r="F112" s="42" t="s">
-        <v>881</v>
+        <v>723</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="60" t="s">
-        <v>882</v>
+        <v>724</v>
       </c>
       <c r="B113" s="42" t="s">
-        <v>883</v>
+        <v>725</v>
       </c>
       <c r="C113" s="42" t="s">
-        <v>884</v>
+        <v>726</v>
       </c>
       <c r="D113" s="42" t="s">
-        <v>885</v>
+        <v>727</v>
       </c>
       <c r="E113" s="42" t="s">
-        <v>886</v>
+        <v>728</v>
       </c>
       <c r="F113" s="42" t="s">
-        <v>887</v>
+        <v>729</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="60" t="s">
-        <v>888</v>
+        <v>730</v>
       </c>
       <c r="B114" s="42" t="s">
-        <v>889</v>
+        <v>731</v>
       </c>
       <c r="C114" s="42" t="s">
-        <v>890</v>
+        <v>732</v>
       </c>
       <c r="D114" s="42" t="s">
-        <v>891</v>
+        <v>733</v>
       </c>
       <c r="E114" s="42" t="s">
-        <v>892</v>
+        <v>734</v>
       </c>
       <c r="F114" s="42" t="s">
-        <v>893</v>
+        <v>735</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="60" t="s">
-        <v>894</v>
+        <v>736</v>
       </c>
       <c r="B115" s="42" t="s">
-        <v>895</v>
+        <v>737</v>
       </c>
       <c r="C115" s="42" t="s">
-        <v>896</v>
+        <v>738</v>
       </c>
       <c r="D115" s="42" t="s">
-        <v>897</v>
+        <v>739</v>
       </c>
       <c r="E115" s="42" t="s">
-        <v>898</v>
+        <v>740</v>
       </c>
       <c r="F115" s="42" t="s">
-        <v>899</v>
+        <v>741</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="60" t="s">
-        <v>900</v>
+        <v>742</v>
       </c>
       <c r="B116" s="42" t="s">
-        <v>901</v>
+        <v>743</v>
       </c>
       <c r="C116" s="42" t="s">
-        <v>902</v>
+        <v>744</v>
       </c>
       <c r="D116" s="42" t="s">
-        <v>903</v>
+        <v>745</v>
       </c>
       <c r="E116" s="42" t="s">
-        <v>904</v>
+        <v>746</v>
       </c>
       <c r="F116" s="42" t="s">
-        <v>905</v>
+        <v>747</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="60" t="s">
-        <v>906</v>
+        <v>748</v>
       </c>
       <c r="B117" s="42" t="s">
-        <v>907</v>
+        <v>749</v>
       </c>
       <c r="C117" s="42" t="s">
-        <v>908</v>
+        <v>750</v>
       </c>
       <c r="D117" s="42" t="s">
-        <v>909</v>
+        <v>751</v>
       </c>
       <c r="E117" s="42" t="s">
-        <v>910</v>
+        <v>752</v>
       </c>
       <c r="F117" s="42" t="s">
-        <v>911</v>
+        <v>753</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="60" t="s">
-        <v>912</v>
+        <v>754</v>
       </c>
       <c r="B118" s="42" t="s">
-        <v>913</v>
+        <v>755</v>
       </c>
       <c r="C118" s="42" t="s">
-        <v>914</v>
+        <v>756</v>
       </c>
       <c r="D118" s="42" t="s">
-        <v>915</v>
+        <v>757</v>
       </c>
       <c r="E118" s="42" t="s">
-        <v>916</v>
+        <v>758</v>
       </c>
       <c r="F118" s="42" t="s">
-        <v>917</v>
+        <v>759</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="60" t="s">
-        <v>918</v>
+        <v>760</v>
       </c>
       <c r="B119" s="42" t="s">
-        <v>919</v>
+        <v>761</v>
       </c>
       <c r="C119" s="42" t="s">
-        <v>920</v>
+        <v>762</v>
       </c>
       <c r="D119" s="42" t="s">
-        <v>921</v>
+        <v>763</v>
       </c>
       <c r="E119" s="42" t="s">
-        <v>922</v>
+        <v>764</v>
       </c>
       <c r="F119" s="42" t="s">
-        <v>923</v>
+        <v>765</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="60" t="s">
-        <v>924</v>
+        <v>766</v>
       </c>
       <c r="B120" s="42" t="s">
-        <v>925</v>
+        <v>767</v>
       </c>
       <c r="C120" s="42" t="s">
-        <v>926</v>
+        <v>768</v>
       </c>
       <c r="D120" s="42" t="s">
-        <v>927</v>
+        <v>769</v>
       </c>
       <c r="E120" s="42" t="s">
-        <v>928</v>
+        <v>770</v>
       </c>
       <c r="F120" s="42" t="s">
-        <v>929</v>
+        <v>771</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="60" t="s">
-        <v>930</v>
+        <v>772</v>
       </c>
       <c r="B121" s="42" t="s">
-        <v>931</v>
+        <v>773</v>
       </c>
       <c r="C121" s="42" t="s">
-        <v>932</v>
+        <v>774</v>
       </c>
       <c r="D121" s="42" t="s">
-        <v>933</v>
+        <v>775</v>
       </c>
       <c r="E121" s="42" t="s">
-        <v>934</v>
+        <v>776</v>
       </c>
       <c r="F121" s="42" t="s">
-        <v>935</v>
+        <v>777</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="60" t="s">
-        <v>936</v>
+        <v>778</v>
       </c>
       <c r="B122" s="42" t="s">
-        <v>937</v>
+        <v>779</v>
       </c>
       <c r="C122" s="42" t="s">
-        <v>938</v>
+        <v>780</v>
       </c>
       <c r="D122" s="42" t="s">
-        <v>939</v>
+        <v>781</v>
       </c>
       <c r="E122" s="42" t="s">
-        <v>940</v>
+        <v>782</v>
       </c>
       <c r="F122" s="42" t="s">
-        <v>941</v>
+        <v>783</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="60" t="s">
-        <v>942</v>
+        <v>784</v>
       </c>
       <c r="B123" s="42" t="s">
-        <v>943</v>
+        <v>785</v>
       </c>
       <c r="C123" s="42" t="s">
-        <v>944</v>
+        <v>786</v>
       </c>
       <c r="D123" s="42" t="s">
-        <v>945</v>
+        <v>787</v>
       </c>
       <c r="E123" s="42" t="s">
-        <v>946</v>
+        <v>788</v>
       </c>
       <c r="F123" s="42" t="s">
-        <v>947</v>
+        <v>789</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="60" t="s">
-        <v>948</v>
+        <v>790</v>
       </c>
       <c r="B124" s="42" t="s">
-        <v>949</v>
+        <v>791</v>
       </c>
       <c r="C124" s="42" t="s">
-        <v>950</v>
+        <v>792</v>
       </c>
       <c r="D124" s="42" t="s">
-        <v>951</v>
+        <v>793</v>
       </c>
       <c r="E124" s="42" t="s">
-        <v>952</v>
+        <v>794</v>
       </c>
       <c r="F124" s="42" t="s">
-        <v>953</v>
+        <v>795</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="60" t="s">
-        <v>954</v>
+        <v>796</v>
       </c>
       <c r="B125" s="42" t="s">
-        <v>955</v>
+        <v>797</v>
       </c>
       <c r="C125" s="42" t="s">
-        <v>956</v>
+        <v>798</v>
       </c>
       <c r="D125" s="42" t="s">
-        <v>957</v>
+        <v>799</v>
       </c>
       <c r="E125" s="42" t="s">
-        <v>958</v>
+        <v>800</v>
       </c>
       <c r="F125" s="42" t="s">
-        <v>959</v>
+        <v>801</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12511,19 +11582,19 @@
         <v>404</v>
       </c>
       <c r="B126" s="42" t="s">
-        <v>960</v>
+        <v>802</v>
       </c>
       <c r="C126" s="42" t="s">
-        <v>961</v>
+        <v>803</v>
       </c>
       <c r="D126" s="42" t="s">
-        <v>962</v>
+        <v>804</v>
       </c>
       <c r="E126" s="42" t="s">
-        <v>963</v>
+        <v>805</v>
       </c>
       <c r="F126" s="42" t="s">
-        <v>964</v>
+        <v>806</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12531,19 +11602,19 @@
         <v>410</v>
       </c>
       <c r="B127" s="42" t="s">
-        <v>965</v>
+        <v>807</v>
       </c>
       <c r="C127" s="42" t="s">
-        <v>966</v>
+        <v>808</v>
       </c>
       <c r="D127" s="42" t="s">
-        <v>967</v>
+        <v>809</v>
       </c>
       <c r="E127" s="42" t="s">
-        <v>968</v>
+        <v>810</v>
       </c>
       <c r="F127" s="42" t="s">
-        <v>969</v>
+        <v>811</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12551,19 +11622,19 @@
         <v>416</v>
       </c>
       <c r="B128" s="42" t="s">
-        <v>970</v>
+        <v>812</v>
       </c>
       <c r="C128" s="42" t="s">
-        <v>971</v>
+        <v>813</v>
       </c>
       <c r="D128" s="42" t="s">
-        <v>972</v>
+        <v>814</v>
       </c>
       <c r="E128" s="42" t="s">
-        <v>973</v>
+        <v>815</v>
       </c>
       <c r="F128" s="42" t="s">
-        <v>974</v>
+        <v>816</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12571,39 +11642,39 @@
         <v>422</v>
       </c>
       <c r="B129" s="42" t="s">
-        <v>975</v>
+        <v>817</v>
       </c>
       <c r="C129" s="42" t="s">
-        <v>976</v>
+        <v>818</v>
       </c>
       <c r="D129" s="42" t="s">
-        <v>977</v>
+        <v>819</v>
       </c>
       <c r="E129" s="42" t="s">
-        <v>978</v>
+        <v>820</v>
       </c>
       <c r="F129" s="42" t="s">
-        <v>979</v>
+        <v>821</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="60" t="s">
-        <v>980</v>
+        <v>822</v>
       </c>
       <c r="B130" s="42" t="s">
-        <v>981</v>
+        <v>823</v>
       </c>
       <c r="C130" s="42" t="s">
-        <v>982</v>
+        <v>824</v>
       </c>
       <c r="D130" s="42" t="s">
-        <v>983</v>
+        <v>825</v>
       </c>
       <c r="E130" s="42" t="s">
-        <v>984</v>
+        <v>826</v>
       </c>
       <c r="F130" s="42" t="s">
-        <v>985</v>
+        <v>827</v>
       </c>
     </row>
   </sheetData>
@@ -12651,7 +11722,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="81" t="s">
-        <v>986</v>
+        <v>828</v>
       </c>
       <c r="G1" s="63"/>
       <c r="H1" s="63"/>
@@ -12663,13 +11734,13 @@
       <c r="A2" s="82"/>
       <c r="B2" s="83"/>
       <c r="C2" s="83" t="s">
-        <v>987</v>
+        <v>829</v>
       </c>
       <c r="D2" s="83" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="83" t="s">
-        <v>988</v>
+        <v>830</v>
       </c>
       <c r="F2" s="84"/>
       <c r="G2" s="63"/>
@@ -12681,16 +11752,16 @@
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="82"/>
       <c r="B3" s="83" t="s">
-        <v>989</v>
+        <v>831</v>
       </c>
       <c r="C3" s="85" t="s">
-        <v>990</v>
+        <v>832</v>
       </c>
       <c r="D3" s="83" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="83" t="s">
-        <v>988</v>
+        <v>830</v>
       </c>
       <c r="F3" s="84"/>
       <c r="G3" s="63"/>
@@ -12702,16 +11773,16 @@
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="82"/>
       <c r="B4" s="83" t="s">
-        <v>991</v>
+        <v>833</v>
       </c>
       <c r="C4" s="85" t="s">
-        <v>992</v>
+        <v>834</v>
       </c>
       <c r="D4" s="83" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="83" t="s">
-        <v>993</v>
+        <v>835</v>
       </c>
       <c r="F4" s="84"/>
       <c r="G4" s="63"/>
@@ -12723,16 +11794,16 @@
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="82"/>
       <c r="B5" s="83" t="s">
-        <v>994</v>
+        <v>836</v>
       </c>
       <c r="C5" s="85" t="s">
-        <v>990</v>
+        <v>832</v>
       </c>
       <c r="D5" s="83" t="s">
-        <v>993</v>
+        <v>835</v>
       </c>
       <c r="E5" s="83" t="s">
-        <v>988</v>
+        <v>830</v>
       </c>
       <c r="F5" s="84"/>
       <c r="G5" s="63"/>
@@ -12744,16 +11815,16 @@
     <row r="6" s="1" customFormat="true" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="82"/>
       <c r="B6" s="83" t="s">
-        <v>995</v>
+        <v>837</v>
       </c>
       <c r="C6" s="85" t="s">
-        <v>996</v>
+        <v>838</v>
       </c>
       <c r="D6" s="83" t="s">
-        <v>993</v>
+        <v>835</v>
       </c>
       <c r="E6" s="85" t="s">
-        <v>997</v>
+        <v>839</v>
       </c>
       <c r="F6" s="84"/>
       <c r="G6" s="63"/>
@@ -12764,19 +11835,19 @@
     </row>
     <row r="7" s="1" customFormat="true" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="82" t="s">
-        <v>998</v>
+        <v>840</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>999</v>
+        <v>841</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>1000</v>
+        <v>842</v>
       </c>
       <c r="D7" s="87" t="s">
-        <v>1001</v>
+        <v>843</v>
       </c>
       <c r="E7" s="87" t="s">
-        <v>1002</v>
+        <v>844</v>
       </c>
       <c r="F7" s="84"/>
       <c r="G7" s="64"/>
@@ -12787,16 +11858,16 @@
         <v>74</v>
       </c>
       <c r="B8" s="86" t="s">
-        <v>1003</v>
+        <v>845</v>
       </c>
       <c r="C8" s="87" t="s">
-        <v>1004</v>
+        <v>846</v>
       </c>
       <c r="D8" s="87" t="s">
-        <v>1001</v>
+        <v>843</v>
       </c>
       <c r="E8" s="87" t="s">
-        <v>1005</v>
+        <v>847</v>
       </c>
       <c r="F8" s="84"/>
       <c r="G8" s="63"/>
@@ -12810,16 +11881,16 @@
         <v>74</v>
       </c>
       <c r="B9" s="86" t="s">
-        <v>1006</v>
+        <v>848</v>
       </c>
       <c r="C9" s="87" t="s">
-        <v>1000</v>
+        <v>842</v>
       </c>
       <c r="D9" s="87" t="s">
-        <v>1005</v>
+        <v>847</v>
       </c>
       <c r="E9" s="87" t="s">
-        <v>1007</v>
+        <v>849</v>
       </c>
       <c r="F9" s="84"/>
       <c r="G9" s="63"/>
@@ -12833,16 +11904,16 @@
         <v>25</v>
       </c>
       <c r="B10" s="89" t="s">
-        <v>1008</v>
+        <v>850</v>
       </c>
       <c r="C10" s="90" t="s">
-        <v>1009</v>
+        <v>851</v>
       </c>
       <c r="D10" s="90" t="s">
-        <v>1001</v>
+        <v>843</v>
       </c>
       <c r="E10" s="90" t="s">
-        <v>1010</v>
+        <v>852</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="63"/>
@@ -12856,16 +11927,16 @@
         <v>25</v>
       </c>
       <c r="B11" s="92" t="s">
-        <v>1011</v>
+        <v>853</v>
       </c>
       <c r="C11" s="93" t="s">
-        <v>1000</v>
+        <v>842</v>
       </c>
       <c r="D11" s="93" t="s">
-        <v>1010</v>
+        <v>852</v>
       </c>
       <c r="E11" s="93" t="s">
-        <v>1012</v>
+        <v>854</v>
       </c>
       <c r="F11" s="94"/>
       <c r="G11" s="63"/>
@@ -12879,17 +11950,17 @@
         <v>25</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>1013</v>
+        <v>855</v>
       </c>
       <c r="C12" s="93" t="s">
-        <v>1014</v>
+        <v>856</v>
       </c>
       <c r="D12" s="93" t="s">
-        <v>1015</v>
+        <v>857</v>
       </c>
       <c r="E12" s="93"/>
       <c r="F12" s="95" t="s">
-        <v>1016</v>
+        <v>858</v>
       </c>
       <c r="G12" s="63"/>
       <c r="H12" s="63"/>
@@ -12902,13 +11973,13 @@
         <v>25</v>
       </c>
       <c r="B13" s="93" t="s">
-        <v>1017</v>
+        <v>859</v>
       </c>
       <c r="C13" s="93" t="s">
-        <v>1018</v>
+        <v>860</v>
       </c>
       <c r="D13" s="93" t="s">
-        <v>1019</v>
+        <v>861</v>
       </c>
       <c r="E13" s="93"/>
       <c r="F13" s="95"/>
@@ -12949,16 +12020,16 @@
         <v>47</v>
       </c>
       <c r="B16" s="90" t="s">
-        <v>1020</v>
+        <v>862</v>
       </c>
       <c r="C16" s="90" t="s">
-        <v>1004</v>
+        <v>846</v>
       </c>
       <c r="D16" s="90" t="s">
-        <v>1021</v>
+        <v>863</v>
       </c>
       <c r="E16" s="90" t="s">
-        <v>1022</v>
+        <v>864</v>
       </c>
       <c r="F16" s="102"/>
       <c r="G16" s="63"/>
@@ -12972,16 +12043,16 @@
         <v>47</v>
       </c>
       <c r="B17" s="93" t="s">
-        <v>1023</v>
+        <v>865</v>
       </c>
       <c r="C17" s="93" t="s">
-        <v>1000</v>
+        <v>842</v>
       </c>
       <c r="D17" s="93" t="s">
-        <v>1022</v>
+        <v>864</v>
       </c>
       <c r="E17" s="93" t="s">
-        <v>1024</v>
+        <v>866</v>
       </c>
       <c r="F17" s="95"/>
       <c r="G17" s="63"/>
@@ -12995,17 +12066,17 @@
         <v>47</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>1025</v>
+        <v>867</v>
       </c>
       <c r="C18" s="104" t="s">
-        <v>1014</v>
+        <v>856</v>
       </c>
       <c r="D18" s="104" t="s">
-        <v>1026</v>
+        <v>868</v>
       </c>
       <c r="E18" s="104"/>
       <c r="F18" s="105" t="s">
-        <v>1027</v>
+        <v>869</v>
       </c>
       <c r="G18" s="63"/>
       <c r="H18" s="63"/>
@@ -13018,13 +12089,13 @@
         <v>47</v>
       </c>
       <c r="B19" s="97" t="s">
-        <v>1028</v>
+        <v>870</v>
       </c>
       <c r="C19" s="97" t="s">
-        <v>1018</v>
+        <v>860</v>
       </c>
       <c r="D19" s="97" t="s">
-        <v>1029</v>
+        <v>871</v>
       </c>
       <c r="E19" s="97"/>
       <c r="F19" s="98"/>
@@ -13065,16 +12136,16 @@
         <v>36</v>
       </c>
       <c r="B22" s="89" t="s">
-        <v>1030</v>
+        <v>872</v>
       </c>
       <c r="C22" s="90" t="s">
-        <v>1009</v>
+        <v>851</v>
       </c>
       <c r="D22" s="90" t="s">
-        <v>1001</v>
+        <v>843</v>
       </c>
       <c r="E22" s="90" t="s">
-        <v>1031</v>
+        <v>873</v>
       </c>
       <c r="F22" s="24"/>
       <c r="G22" s="63"/>
@@ -13088,16 +12159,16 @@
         <v>36</v>
       </c>
       <c r="B23" s="92" t="s">
-        <v>1032</v>
+        <v>874</v>
       </c>
       <c r="C23" s="93" t="s">
-        <v>1000</v>
+        <v>842</v>
       </c>
       <c r="D23" s="93" t="s">
-        <v>1031</v>
+        <v>873</v>
       </c>
       <c r="E23" s="93" t="s">
-        <v>1033</v>
+        <v>875</v>
       </c>
       <c r="F23" s="94"/>
       <c r="G23" s="63"/>
@@ -13111,17 +12182,17 @@
         <v>36</v>
       </c>
       <c r="B24" s="104" t="s">
-        <v>1034</v>
+        <v>876</v>
       </c>
       <c r="C24" s="104" t="s">
-        <v>1014</v>
+        <v>856</v>
       </c>
       <c r="D24" s="104" t="s">
-        <v>1035</v>
+        <v>877</v>
       </c>
       <c r="E24" s="104"/>
       <c r="F24" s="105" t="s">
-        <v>1036</v>
+        <v>878</v>
       </c>
       <c r="G24" s="63"/>
       <c r="H24" s="63"/>
@@ -13134,13 +12205,13 @@
         <v>36</v>
       </c>
       <c r="B25" s="97" t="s">
-        <v>1037</v>
+        <v>879</v>
       </c>
       <c r="C25" s="97" t="s">
-        <v>1018</v>
+        <v>860</v>
       </c>
       <c r="D25" s="97" t="s">
-        <v>1038</v>
+        <v>880</v>
       </c>
       <c r="E25" s="97"/>
       <c r="F25" s="98"/>
@@ -13181,16 +12252,16 @@
         <v>58</v>
       </c>
       <c r="B28" s="90" t="s">
-        <v>1039</v>
+        <v>881</v>
       </c>
       <c r="C28" s="90" t="s">
-        <v>1004</v>
+        <v>846</v>
       </c>
       <c r="D28" s="90" t="s">
-        <v>1040</v>
+        <v>882</v>
       </c>
       <c r="E28" s="90" t="s">
-        <v>1041</v>
+        <v>883</v>
       </c>
       <c r="F28" s="102"/>
       <c r="G28" s="63"/>
@@ -13204,16 +12275,16 @@
         <v>58</v>
       </c>
       <c r="B29" s="93" t="s">
-        <v>1042</v>
+        <v>884</v>
       </c>
       <c r="C29" s="93" t="s">
-        <v>1000</v>
+        <v>842</v>
       </c>
       <c r="D29" s="93" t="s">
-        <v>1041</v>
+        <v>883</v>
       </c>
       <c r="E29" s="93" t="s">
-        <v>1043</v>
+        <v>885</v>
       </c>
       <c r="F29" s="95"/>
       <c r="G29" s="63"/>
@@ -13227,17 +12298,17 @@
         <v>58</v>
       </c>
       <c r="B30" s="104" t="s">
-        <v>1044</v>
+        <v>886</v>
       </c>
       <c r="C30" s="104" t="s">
-        <v>1014</v>
+        <v>856</v>
       </c>
       <c r="D30" s="104" t="s">
-        <v>1045</v>
+        <v>887</v>
       </c>
       <c r="E30" s="104"/>
       <c r="F30" s="105" t="s">
-        <v>1046</v>
+        <v>888</v>
       </c>
       <c r="G30" s="63"/>
       <c r="H30" s="63"/>
@@ -13250,13 +12321,13 @@
         <v>58</v>
       </c>
       <c r="B31" s="97" t="s">
-        <v>1047</v>
+        <v>889</v>
       </c>
       <c r="C31" s="97" t="s">
-        <v>1018</v>
+        <v>860</v>
       </c>
       <c r="D31" s="97" t="s">
-        <v>1048</v>
+        <v>890</v>
       </c>
       <c r="E31" s="97"/>
       <c r="F31" s="98"/>
@@ -13395,13 +12466,13 @@
         <v>69</v>
       </c>
       <c r="C1" s="66" t="s">
-        <v>1049</v>
+        <v>891</v>
       </c>
       <c r="D1" s="66" t="s">
         <v>71</v>
       </c>
       <c r="E1" s="66" t="s">
-        <v>1050</v>
+        <v>892</v>
       </c>
       <c r="F1" s="66" t="s">
         <v>25</v>
@@ -13420,7 +12491,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>1051</v>
+        <v>893</v>
       </c>
       <c r="B2" s="41" t="n">
         <v>0</v>
@@ -13450,7 +12521,7 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>1052</v>
+        <v>894</v>
       </c>
       <c r="B3" s="41" t="n">
         <v>1</v>
@@ -13480,7 +12551,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>1053</v>
+        <v>895</v>
       </c>
       <c r="B4" s="41" t="n">
         <v>2</v>
@@ -13510,7 +12581,7 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>1054</v>
+        <v>896</v>
       </c>
       <c r="B5" s="41" t="n">
         <v>3</v>
@@ -13570,7 +12641,7 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>1055</v>
+        <v>897</v>
       </c>
       <c r="B7" s="41" t="n">
         <v>5</v>
@@ -13600,7 +12671,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>1056</v>
+        <v>898</v>
       </c>
       <c r="B8" s="41" t="n">
         <v>6</v>
@@ -13660,7 +12731,7 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="40" t="s">
-        <v>1057</v>
+        <v>899</v>
       </c>
       <c r="B10" s="41" t="n">
         <v>8</v>
@@ -13690,7 +12761,7 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="40" t="s">
-        <v>1058</v>
+        <v>900</v>
       </c>
       <c r="B11" s="41" t="n">
         <v>9</v>
@@ -13720,7 +12791,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>1059</v>
+        <v>901</v>
       </c>
       <c r="B12" s="41" t="n">
         <v>10</v>
@@ -13750,7 +12821,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="40" t="s">
-        <v>1060</v>
+        <v>902</v>
       </c>
       <c r="B13" s="41" t="n">
         <v>11</v>
@@ -13780,7 +12851,7 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="s">
-        <v>1061</v>
+        <v>903</v>
       </c>
       <c r="B14" s="41" t="n">
         <v>12</v>
@@ -14173,7 +13244,7 @@
       <c r="J38" s="42"/>
       <c r="K38" s="42"/>
     </row>
-    <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
         <v>20</v>
       </c>

--- a/TFG_MODELOS_SIMPLES_MEJORADO/02_datasets/metadata/METADATA.xlsx
+++ b/TFG_MODELOS_SIMPLES_MEJORADO/02_datasets/metadata/METADATA.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="1077">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -1524,6 +1524,84 @@
     <t xml:space="preserve">Heartbleed</t>
   </si>
   <si>
+    <t xml:space="preserve">PCA33 + KNN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994769 ± 0.000054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994784 ± 0.000065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994764 ± 0.000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881581 ± 0.035758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811875 ± 0.017249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829280 ± 0.023543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982642 ± 0.000185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nan ± nan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCA33 + Logistic Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973436 ± 0.000214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.974907 ± 0.000261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972855 ± 0.000216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624139 ± 0.044245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507304 ± 0.031815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522715 ± 0.030129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912882 ± 0.000724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCA33 + MLP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986782 ± 0.001005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986845 ± 0.001229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986272 ± 0.001149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883063 ± 0.026216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701158 ± 0.007813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722538 ± 0.004420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955960 ± 0.003459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUS/SMOTE + PCA33 + KNN</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.960031 ± 0.000755</t>
   </si>
   <si>
@@ -1545,7 +1623,55 @@
     <t xml:space="preserve">0.885895 ± 0.001867</t>
   </si>
   <si>
-    <t xml:space="preserve">nan ± nan</t>
+    <t xml:space="preserve">RUS/SMOTE + PCA33 + Logistic Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825662 ± 0.020466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957729 ± 0.000649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877188 ± 0.013217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344565 ± 0.010577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889467 ± 0.014650</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415511 ± 0.012082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658990 ± 0.022764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUS/SMOTE + PCA33 + MLP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934389 ± 0.009397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967087 ± 0.001780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946913 ± 0.006260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482532 ± 0.025358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834625 ± 0.037214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560263 ± 0.021758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828040 ± 0.019412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NearMiss/SMOTE + PCA33 + KNN</t>
   </si>
   <si>
     <t xml:space="preserve">0.470103 ± 0.031386</t>
@@ -1569,6 +1695,9 @@
     <t xml:space="preserve">0.330330 ± 0.023806</t>
   </si>
   <si>
+    <t xml:space="preserve">NearMiss/SMOTE + PCA33 + Logistic Regression</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.169174 ± 0.024350</t>
   </si>
   <si>
@@ -1590,6 +1719,33 @@
     <t xml:space="preserve">0.238517 ± 0.045900</t>
   </si>
   <si>
+    <t xml:space="preserve">NearMiss/SMOTE + PCA33 + MLP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172598 ± 0.019049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918075 ± 0.011387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.183258 ± 0.015787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.217028 ± 0.022895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782404 ± 0.055807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.188048 ± 0.031477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.222533 ± 0.043822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUS/SMOTE + ENN + PCA33 + KNN</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.962029 ± 0.000904</t>
   </si>
   <si>
@@ -1611,6 +1767,57 @@
     <t xml:space="preserve">0.890042 ± 0.002287</t>
   </si>
   <si>
+    <t xml:space="preserve">RUS/SMOTE + ENN + PCA33 + Logistic Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837068 ± 0.023533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959375 ± 0.001558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885263 ± 0.015343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343139 ± 0.015256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886250 ± 0.014289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415738 ± 0.018497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.672420 ± 0.027046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUS/SMOTE + ENN + PCA33 + MLP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938249 ± 0.007336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969328 ± 0.001945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950440 ± 0.005092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489865 ± 0.028581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886763 ± 0.033106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560959 ± 0.026240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835977 ± 0.015443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NearMiss/SMOTE + ENN + PCA33 + KNN</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.493727 ± 0.018957</t>
   </si>
   <si>
@@ -1632,6 +1839,126 @@
     <t xml:space="preserve">0.342626 ± 0.028628</t>
   </si>
   <si>
+    <t xml:space="preserve">NearMiss/SMOTE + ENN + PCA33 + Logistic Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160042 ± 0.020540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886791 ± 0.063082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.176724 ± 0.017080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.237491 ± 0.029441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776043 ± 0.023720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.222630 ± 0.046030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.214233 ± 0.035003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NearMiss/SMOTE + ENN + PCA33 + MLP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173967 ± 0.019998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929946 ± 0.016933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.192613 ± 0.019720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.240715 ± 0.036371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780449 ± 0.055907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.205199 ± 0.045827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.224327 ± 0.047157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.636128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.669882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999028</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.960378</t>
   </si>
   <si>
@@ -1656,6 +1983,54 @@
     <t xml:space="preserve">0.988174</t>
   </si>
   <si>
+    <t xml:space="preserve">0.841457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.677372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996785</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.499205</t>
   </si>
   <si>
@@ -1680,6 +2055,54 @@
     <t xml:space="preserve">0.750053</t>
   </si>
   <si>
+    <t xml:space="preserve">0.170755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.182578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.237699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.229706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.180455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.195069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.233508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.207664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836473</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.962805</t>
   </si>
   <si>
@@ -1704,6 +2127,54 @@
     <t xml:space="preserve">0.988065</t>
   </si>
   <si>
+    <t xml:space="preserve">0.851000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.539182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997093</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.501085</t>
   </si>
   <si>
@@ -1726,6 +2197,54 @@
   </si>
   <si>
     <t xml:space="preserve">0.750992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.187294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.247296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.183430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.204187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.230134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858156</t>
   </si>
   <si>
     <t xml:space="preserve">COMPONENTES DEL PCA POR COLUMNAS</t>
@@ -2961,8 +3480,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="[$-1809]0.000"/>
+    <numFmt numFmtId="167" formatCode="[$-1009]0.000"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -3049,7 +3571,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3078,6 +3600,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF77BC65"/>
         <bgColor rgb="FF81D41A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -3275,7 +3803,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="121">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3592,6 +4120,34 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3604,27 +4160,27 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3810,14 +4366,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>151200</xdr:rowOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>16200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>307440</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>84240</xdr:rowOff>
+      <xdr:colOff>306360</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>159120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3830,8 +4386,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15723720" y="18970200"/>
-          <a:ext cx="5221800" cy="3890160"/>
+          <a:off x="13852440" y="18970200"/>
+          <a:ext cx="4635720" cy="3889080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3847,14 +4403,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>69840</xdr:rowOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>145800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>307440</xdr:colOff>
-      <xdr:row>122</xdr:row>
-      <xdr:rowOff>1080</xdr:rowOff>
+      <xdr:colOff>306360</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>76320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3867,8 +4423,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15723720" y="23262480"/>
-          <a:ext cx="5221800" cy="3888720"/>
+          <a:off x="13852440" y="23262480"/>
+          <a:ext cx="4635720" cy="3887640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3884,14 +4440,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>197280</xdr:rowOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>65160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>307440</xdr:colOff>
-      <xdr:row>142</xdr:row>
-      <xdr:rowOff>150840</xdr:rowOff>
+      <xdr:colOff>306360</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>7920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3904,8 +4460,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15723720" y="27555480"/>
-          <a:ext cx="5221800" cy="3888720"/>
+          <a:off x="13852440" y="27555480"/>
+          <a:ext cx="4635720" cy="3887640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3921,14 +4477,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>151200</xdr:rowOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>16200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>331200</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>82800</xdr:rowOff>
+      <xdr:colOff>330120</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>157680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3941,8 +4497,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21906360" y="18970200"/>
-          <a:ext cx="5219280" cy="3888720"/>
+          <a:off x="19298880" y="18970200"/>
+          <a:ext cx="4635360" cy="3887640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3958,14 +4514,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>69840</xdr:rowOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>145800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>331200</xdr:colOff>
-      <xdr:row>122</xdr:row>
-      <xdr:rowOff>1080</xdr:rowOff>
+      <xdr:colOff>330120</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>76320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3978,8 +4534,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21906360" y="23262480"/>
-          <a:ext cx="5219280" cy="3888720"/>
+          <a:off x="19298880" y="23262480"/>
+          <a:ext cx="4635360" cy="3887640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4005,9 +4561,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>846360</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>101520</xdr:rowOff>
+      <xdr:colOff>845280</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>195480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4020,8 +4576,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14133960" y="28371960"/>
-          <a:ext cx="5654520" cy="3891600"/>
+          <a:off x="12450960" y="28750320"/>
+          <a:ext cx="5082120" cy="3890520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4038,13 +4594,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>107</xdr:row>
-      <xdr:rowOff>20880</xdr:rowOff>
+      <xdr:rowOff>116280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>403560</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>163440</xdr:rowOff>
+      <xdr:colOff>402480</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>106560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4057,8 +4613,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14133960" y="32807880"/>
-          <a:ext cx="5211720" cy="3891600"/>
+          <a:off x="12450960" y="34227720"/>
+          <a:ext cx="4639320" cy="3890520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4074,14 +4630,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>127</xdr:row>
-      <xdr:rowOff>149760</xdr:rowOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>81000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>403560</xdr:colOff>
-      <xdr:row>146</xdr:row>
-      <xdr:rowOff>135000</xdr:rowOff>
+      <xdr:colOff>402480</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>68040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4094,8 +4650,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14133960" y="37102320"/>
-          <a:ext cx="5211720" cy="3891600"/>
+          <a:off x="12450960" y="39134160"/>
+          <a:ext cx="4639320" cy="3890520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4115,10 +4671,10 @@
       <xdr:rowOff>147960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>335160</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>101520</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1051560</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>195480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4131,8 +4687,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20526480" y="28371960"/>
-          <a:ext cx="5223240" cy="3891600"/>
+          <a:off x="18083520" y="28750320"/>
+          <a:ext cx="4639320" cy="3890520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4149,13 +4705,13 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>107</xdr:row>
-      <xdr:rowOff>20880</xdr:rowOff>
+      <xdr:rowOff>116280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>335160</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>163440</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1051560</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>106560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4168,8 +4724,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20526480" y="32807880"/>
-          <a:ext cx="5223240" cy="3891600"/>
+          <a:off x="18083520" y="34227720"/>
+          <a:ext cx="4639320" cy="3890520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4190,14 +4746,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1714680</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>426600</xdr:rowOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>64080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>189720</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>69840</xdr:rowOff>
+      <xdr:colOff>188640</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>116280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4211,7 +4767,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1714680" y="21578400"/>
-          <a:ext cx="5475240" cy="3880080"/>
+          <a:ext cx="4641840" cy="3879000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4227,14 +4783,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>362520</xdr:rowOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>747360</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>5760</xdr:rowOff>
+      <xdr:colOff>746280</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>52200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4247,8 +4803,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8468280" y="21514320"/>
-          <a:ext cx="5169600" cy="3880080"/>
+          <a:off x="7461360" y="21514320"/>
+          <a:ext cx="4641840" cy="3879000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4264,14 +4820,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>362520</xdr:rowOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>264600</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>5760</xdr:rowOff>
+      <xdr:colOff>263520</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>52200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4284,8 +4840,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14306400" y="21514320"/>
-          <a:ext cx="5234760" cy="3880080"/>
+          <a:off x="12604680" y="21514320"/>
+          <a:ext cx="4641840" cy="3879000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4301,14 +4857,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1899360</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>157320</xdr:rowOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>374400</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>140400</xdr:rowOff>
+      <xdr:colOff>373320</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>186840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4322,7 +4878,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1899360" y="26161200"/>
-          <a:ext cx="5475240" cy="3880080"/>
+          <a:ext cx="4641840" cy="3879000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4338,14 +4894,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>157320</xdr:rowOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>747360</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>140400</xdr:rowOff>
+      <xdr:colOff>746280</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>186840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4358,8 +4914,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8468280" y="26161200"/>
-          <a:ext cx="5169600" cy="3880080"/>
+          <a:off x="7461360" y="26161200"/>
+          <a:ext cx="4641840" cy="3879000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4987,7 +5543,7 @@
       <c r="E34" s="34"/>
       <c r="F34" s="35"/>
     </row>
-    <row r="35" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
         <v>58</v>
       </c>
@@ -5037,7 +5593,7 @@
       <c r="E38" s="34"/>
       <c r="F38" s="35"/>
     </row>
-    <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="29" t="s">
         <v>64</v>
       </c>
@@ -5082,8 +5638,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -6181,7 +6737,7 @@
       <c r="K36" s="42"/>
       <c r="L36" s="35"/>
     </row>
-    <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="56" t="n">
         <v>17</v>
       </c>
@@ -6217,7 +6773,7 @@
       <c r="K38" s="42"/>
       <c r="L38" s="35"/>
     </row>
-    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
         <v>20</v>
       </c>
@@ -6700,7 +7256,7 @@
       <c r="J69" s="42"/>
       <c r="K69" s="42"/>
     </row>
-    <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
         <v>17</v>
       </c>
@@ -6734,7 +7290,7 @@
       <c r="J71" s="42"/>
       <c r="K71" s="42"/>
     </row>
-    <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
         <v>20</v>
       </c>
@@ -7854,8 +8410,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -8458,8 +9014,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -8483,9 +9039,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="42" width="21.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="35" width="17.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="35" width="19.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="18.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="20.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="17.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="17.99"/>
   </cols>
   <sheetData>
-    <row r="1" s="71" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="71" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="65" t="s">
         <v>68</v>
       </c>
@@ -9147,7 +9707,7 @@
       <c r="AN11" s="35"/>
       <c r="AO11" s="35"/>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="72" t="s">
         <v>489</v>
       </c>
@@ -9457,22 +10017,52 @@
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
-      <c r="Z26" s="1"/>
-      <c r="AA26" s="1"/>
-      <c r="AB26" s="1"/>
-      <c r="AC26" s="1"/>
-      <c r="AD26" s="1"/>
+      <c r="O26" s="79"/>
+      <c r="P26" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" s="54" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" s="54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="V26" s="54" t="n">
+        <v>6</v>
+      </c>
+      <c r="W26" s="54" t="n">
+        <v>7</v>
+      </c>
+      <c r="X26" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y26" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z26" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA26" s="54" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB26" s="54" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC26" s="54" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD26" s="54" t="n">
+        <v>14</v>
+      </c>
       <c r="AE26" s="1"/>
       <c r="AF26" s="1"/>
       <c r="AG26" s="1"/>
@@ -9492,36 +10082,86 @@
         <v>1</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42"/>
+        <v>494</v>
+      </c>
+      <c r="C27" s="80" t="s">
+        <v>495</v>
+      </c>
+      <c r="D27" s="80" t="s">
+        <v>496</v>
+      </c>
+      <c r="E27" s="80" t="s">
+        <v>495</v>
+      </c>
+      <c r="F27" s="80" t="s">
+        <v>497</v>
+      </c>
+      <c r="G27" s="80" t="s">
+        <v>498</v>
+      </c>
+      <c r="H27" s="80" t="s">
+        <v>499</v>
+      </c>
+      <c r="I27" s="81" t="s">
+        <v>500</v>
+      </c>
+      <c r="J27" s="81" t="s">
+        <v>501</v>
+      </c>
+      <c r="K27" s="80" t="s">
+        <v>502</v>
+      </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-      <c r="Z27" s="1"/>
-      <c r="AA27" s="1"/>
-      <c r="AB27" s="1"/>
-      <c r="AC27" s="1"/>
-      <c r="AD27" s="1"/>
+      <c r="O27" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="57" t="n">
+        <v>417654</v>
+      </c>
+      <c r="Q27" s="57" t="n">
+        <v>65</v>
+      </c>
+      <c r="R27" s="57" t="n">
+        <v>23</v>
+      </c>
+      <c r="S27" s="57" t="n">
+        <v>1106</v>
+      </c>
+      <c r="T27" s="57" t="n">
+        <v>33</v>
+      </c>
+      <c r="U27" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="W27" s="57" t="n">
+        <v>11</v>
+      </c>
+      <c r="X27" s="57" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y27" s="57" t="n">
+        <v>88</v>
+      </c>
+      <c r="Z27" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA27" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC27" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
       <c r="AG27" s="1"/>
@@ -9539,36 +10179,86 @@
         <v>2</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" s="42"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="42"/>
+        <v>503</v>
+      </c>
+      <c r="C28" s="80" t="s">
+        <v>504</v>
+      </c>
+      <c r="D28" s="80" t="s">
+        <v>505</v>
+      </c>
+      <c r="E28" s="80" t="s">
+        <v>504</v>
+      </c>
+      <c r="F28" s="80" t="s">
+        <v>506</v>
+      </c>
+      <c r="G28" s="80" t="s">
+        <v>507</v>
+      </c>
+      <c r="H28" s="80" t="s">
+        <v>508</v>
+      </c>
+      <c r="I28" s="81" t="s">
+        <v>509</v>
+      </c>
+      <c r="J28" s="81" t="s">
+        <v>510</v>
+      </c>
+      <c r="K28" s="80" t="s">
+        <v>502</v>
+      </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
-      <c r="AA28" s="1"/>
-      <c r="AB28" s="1"/>
-      <c r="AC28" s="1"/>
-      <c r="AD28" s="1"/>
+      <c r="O28" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="57" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q28" s="57" t="n">
+        <v>34459</v>
+      </c>
+      <c r="R28" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
       <c r="AG28" s="1"/>
@@ -9586,36 +10276,86 @@
         <v>3</v>
       </c>
       <c r="B29" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
+        <v>511</v>
+      </c>
+      <c r="C29" s="80" t="s">
+        <v>512</v>
+      </c>
+      <c r="D29" s="80" t="s">
+        <v>513</v>
+      </c>
+      <c r="E29" s="80" t="s">
+        <v>512</v>
+      </c>
+      <c r="F29" s="80" t="s">
+        <v>514</v>
+      </c>
+      <c r="G29" s="80" t="s">
+        <v>515</v>
+      </c>
+      <c r="H29" s="80" t="s">
+        <v>516</v>
+      </c>
+      <c r="I29" s="81" t="s">
+        <v>517</v>
+      </c>
+      <c r="J29" s="81" t="s">
+        <v>518</v>
+      </c>
+      <c r="K29" s="80" t="s">
+        <v>502</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
-      <c r="AA29" s="1"/>
-      <c r="AB29" s="1"/>
-      <c r="AC29" s="1"/>
-      <c r="AD29" s="1"/>
+      <c r="O29" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="P29" s="57" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q29" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" s="57" t="n">
+        <v>25587</v>
+      </c>
+      <c r="S29" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
       <c r="AG29" s="1"/>
@@ -9633,54 +10373,86 @@
         <v>4</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="42" t="s">
-        <v>494</v>
-      </c>
-      <c r="D30" s="42" t="s">
-        <v>495</v>
-      </c>
-      <c r="E30" s="42" t="s">
-        <v>494</v>
-      </c>
-      <c r="F30" s="42" t="s">
-        <v>496</v>
-      </c>
-      <c r="G30" s="42" t="s">
-        <v>497</v>
-      </c>
-      <c r="H30" s="42" t="s">
-        <v>498</v>
-      </c>
-      <c r="I30" s="42" t="s">
-        <v>499</v>
-      </c>
-      <c r="J30" s="42" t="s">
-        <v>500</v>
-      </c>
-      <c r="K30" s="42" t="s">
-        <v>501</v>
+        <v>519</v>
+      </c>
+      <c r="C30" s="80" t="s">
+        <v>520</v>
+      </c>
+      <c r="D30" s="80" t="s">
+        <v>521</v>
+      </c>
+      <c r="E30" s="80" t="s">
+        <v>520</v>
+      </c>
+      <c r="F30" s="80" t="s">
+        <v>522</v>
+      </c>
+      <c r="G30" s="80" t="s">
+        <v>523</v>
+      </c>
+      <c r="H30" s="80" t="s">
+        <v>524</v>
+      </c>
+      <c r="I30" s="81" t="s">
+        <v>525</v>
+      </c>
+      <c r="J30" s="81" t="s">
+        <v>526</v>
+      </c>
+      <c r="K30" s="80" t="s">
+        <v>502</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
-      <c r="AB30" s="1"/>
-      <c r="AC30" s="1"/>
-      <c r="AD30" s="1"/>
+      <c r="O30" s="54" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" s="57" t="n">
+        <v>635</v>
+      </c>
+      <c r="Q30" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="R30" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="57" t="n">
+        <v>17500</v>
+      </c>
+      <c r="T30" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
       <c r="AG30" s="1"/>
@@ -9698,36 +10470,86 @@
         <v>5</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" s="42"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42"/>
-      <c r="K31" s="42"/>
+        <v>527</v>
+      </c>
+      <c r="C31" s="80" t="s">
+        <v>528</v>
+      </c>
+      <c r="D31" s="80" t="s">
+        <v>529</v>
+      </c>
+      <c r="E31" s="80" t="s">
+        <v>528</v>
+      </c>
+      <c r="F31" s="80" t="s">
+        <v>530</v>
+      </c>
+      <c r="G31" s="80" t="s">
+        <v>531</v>
+      </c>
+      <c r="H31" s="80" t="s">
+        <v>532</v>
+      </c>
+      <c r="I31" s="81" t="s">
+        <v>533</v>
+      </c>
+      <c r="J31" s="81" t="s">
+        <v>534</v>
+      </c>
+      <c r="K31" s="80" t="s">
+        <v>502</v>
+      </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-      <c r="Z31" s="1"/>
-      <c r="AA31" s="1"/>
-      <c r="AB31" s="1"/>
-      <c r="AC31" s="1"/>
-      <c r="AD31" s="1"/>
+      <c r="O31" s="54" t="n">
+        <v>4</v>
+      </c>
+      <c r="P31" s="57" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q31" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="R31" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="57" t="n">
+        <v>2037</v>
+      </c>
+      <c r="U31" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
       <c r="AG31" s="1"/>
@@ -9745,36 +10567,86 @@
         <v>6</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="42"/>
+        <v>535</v>
+      </c>
+      <c r="C32" s="80" t="s">
+        <v>536</v>
+      </c>
+      <c r="D32" s="80" t="s">
+        <v>537</v>
+      </c>
+      <c r="E32" s="80" t="s">
+        <v>536</v>
+      </c>
+      <c r="F32" s="80" t="s">
+        <v>538</v>
+      </c>
+      <c r="G32" s="80" t="s">
+        <v>539</v>
+      </c>
+      <c r="H32" s="80" t="s">
+        <v>540</v>
+      </c>
+      <c r="I32" s="81" t="s">
+        <v>541</v>
+      </c>
+      <c r="J32" s="81" t="s">
+        <v>542</v>
+      </c>
+      <c r="K32" s="80" t="s">
+        <v>502</v>
+      </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
-      <c r="AA32" s="1"/>
-      <c r="AB32" s="1"/>
-      <c r="AC32" s="1"/>
-      <c r="AD32" s="1"/>
+      <c r="O32" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="P32" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="57" t="n">
+        <v>1179</v>
+      </c>
+      <c r="V32" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="AE32" s="1"/>
       <c r="AF32" s="1"/>
       <c r="AG32" s="1"/>
@@ -9792,54 +10664,86 @@
         <v>7</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>108</v>
-      </c>
-      <c r="C33" s="42" t="s">
+        <v>543</v>
+      </c>
+      <c r="C33" s="80" t="s">
+        <v>544</v>
+      </c>
+      <c r="D33" s="80" t="s">
+        <v>545</v>
+      </c>
+      <c r="E33" s="80" t="s">
+        <v>544</v>
+      </c>
+      <c r="F33" s="80" t="s">
+        <v>546</v>
+      </c>
+      <c r="G33" s="80" t="s">
+        <v>547</v>
+      </c>
+      <c r="H33" s="80" t="s">
+        <v>548</v>
+      </c>
+      <c r="I33" s="81" t="s">
+        <v>549</v>
+      </c>
+      <c r="J33" s="81" t="s">
+        <v>550</v>
+      </c>
+      <c r="K33" s="80" t="s">
         <v>502</v>
-      </c>
-      <c r="D33" s="42" t="s">
-        <v>503</v>
-      </c>
-      <c r="E33" s="42" t="s">
-        <v>502</v>
-      </c>
-      <c r="F33" s="42" t="s">
-        <v>504</v>
-      </c>
-      <c r="G33" s="42" t="s">
-        <v>505</v>
-      </c>
-      <c r="H33" s="42" t="s">
-        <v>506</v>
-      </c>
-      <c r="I33" s="42" t="s">
-        <v>507</v>
-      </c>
-      <c r="J33" s="42" t="s">
-        <v>508</v>
-      </c>
-      <c r="K33" s="42" t="s">
-        <v>501</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
-      <c r="Z33" s="1"/>
-      <c r="AA33" s="1"/>
-      <c r="AB33" s="1"/>
-      <c r="AC33" s="1"/>
-      <c r="AD33" s="1"/>
+      <c r="O33" s="54" t="n">
+        <v>6</v>
+      </c>
+      <c r="P33" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="57" t="n">
+        <v>1067</v>
+      </c>
+      <c r="W33" s="57" t="n">
+        <v>7</v>
+      </c>
+      <c r="X33" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
       <c r="AG33" s="1"/>
@@ -9857,54 +10761,86 @@
         <v>8</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="C34" s="42" t="s">
-        <v>509</v>
-      </c>
-      <c r="D34" s="42" t="s">
-        <v>510</v>
-      </c>
-      <c r="E34" s="42" t="s">
-        <v>509</v>
-      </c>
-      <c r="F34" s="42" t="s">
-        <v>511</v>
-      </c>
-      <c r="G34" s="42" t="s">
-        <v>512</v>
-      </c>
-      <c r="H34" s="42" t="s">
-        <v>513</v>
-      </c>
-      <c r="I34" s="42" t="s">
-        <v>514</v>
-      </c>
-      <c r="J34" s="42" t="s">
-        <v>515</v>
-      </c>
-      <c r="K34" s="42" t="s">
-        <v>501</v>
+        <v>551</v>
+      </c>
+      <c r="C34" s="80" t="s">
+        <v>552</v>
+      </c>
+      <c r="D34" s="80" t="s">
+        <v>553</v>
+      </c>
+      <c r="E34" s="80" t="s">
+        <v>552</v>
+      </c>
+      <c r="F34" s="80" t="s">
+        <v>554</v>
+      </c>
+      <c r="G34" s="80" t="s">
+        <v>555</v>
+      </c>
+      <c r="H34" s="80" t="s">
+        <v>556</v>
+      </c>
+      <c r="I34" s="81" t="s">
+        <v>557</v>
+      </c>
+      <c r="J34" s="81" t="s">
+        <v>558</v>
+      </c>
+      <c r="K34" s="80" t="s">
+        <v>502</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
-      <c r="Z34" s="1"/>
-      <c r="AA34" s="1"/>
-      <c r="AB34" s="1"/>
-      <c r="AC34" s="1"/>
-      <c r="AD34" s="1"/>
+      <c r="O34" s="54" t="n">
+        <v>7</v>
+      </c>
+      <c r="P34" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="W34" s="57" t="n">
+        <v>1039</v>
+      </c>
+      <c r="X34" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
       <c r="AG34" s="1"/>
@@ -9922,36 +10858,86 @@
         <v>9</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="42"/>
-      <c r="J35" s="42"/>
-      <c r="K35" s="42"/>
+        <v>559</v>
+      </c>
+      <c r="C35" s="80" t="s">
+        <v>560</v>
+      </c>
+      <c r="D35" s="80" t="s">
+        <v>561</v>
+      </c>
+      <c r="E35" s="80" t="s">
+        <v>560</v>
+      </c>
+      <c r="F35" s="80" t="s">
+        <v>562</v>
+      </c>
+      <c r="G35" s="80" t="s">
+        <v>563</v>
+      </c>
+      <c r="H35" s="80" t="s">
+        <v>564</v>
+      </c>
+      <c r="I35" s="81" t="s">
+        <v>565</v>
+      </c>
+      <c r="J35" s="81" t="s">
+        <v>566</v>
+      </c>
+      <c r="K35" s="80" t="s">
+        <v>502</v>
+      </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
-      <c r="Z35" s="1"/>
-      <c r="AA35" s="1"/>
-      <c r="AB35" s="1"/>
-      <c r="AC35" s="1"/>
-      <c r="AD35" s="1"/>
+      <c r="O35" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="P35" s="57" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q35" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="57" t="n">
+        <v>631</v>
+      </c>
+      <c r="Y35" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA35" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
       <c r="AG35" s="1"/>
@@ -9969,54 +10955,86 @@
         <v>10</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>111</v>
-      </c>
-      <c r="C36" s="42" t="s">
-        <v>516</v>
-      </c>
-      <c r="D36" s="42" t="s">
-        <v>517</v>
-      </c>
-      <c r="E36" s="42" t="s">
-        <v>516</v>
-      </c>
-      <c r="F36" s="42" t="s">
-        <v>518</v>
-      </c>
-      <c r="G36" s="42" t="s">
-        <v>519</v>
-      </c>
-      <c r="H36" s="42" t="s">
-        <v>520</v>
-      </c>
-      <c r="I36" s="42" t="s">
-        <v>521</v>
-      </c>
-      <c r="J36" s="42" t="s">
-        <v>522</v>
-      </c>
-      <c r="K36" s="42" t="s">
-        <v>501</v>
+        <v>567</v>
+      </c>
+      <c r="C36" s="80" t="s">
+        <v>568</v>
+      </c>
+      <c r="D36" s="80" t="s">
+        <v>569</v>
+      </c>
+      <c r="E36" s="80" t="s">
+        <v>568</v>
+      </c>
+      <c r="F36" s="80" t="s">
+        <v>570</v>
+      </c>
+      <c r="G36" s="80" t="s">
+        <v>571</v>
+      </c>
+      <c r="H36" s="80" t="s">
+        <v>572</v>
+      </c>
+      <c r="I36" s="81" t="s">
+        <v>573</v>
+      </c>
+      <c r="J36" s="81" t="s">
+        <v>574</v>
+      </c>
+      <c r="K36" s="80" t="s">
+        <v>502</v>
       </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
-      <c r="W36" s="1"/>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
-      <c r="Z36" s="1"/>
-      <c r="AA36" s="1"/>
-      <c r="AB36" s="1"/>
-      <c r="AC36" s="1"/>
-      <c r="AD36" s="1"/>
+      <c r="O36" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="P36" s="57" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q36" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="57" t="n">
+        <v>272</v>
+      </c>
+      <c r="Z36" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="AE36" s="1"/>
       <c r="AF36" s="1"/>
       <c r="AG36" s="1"/>
@@ -10034,36 +11052,86 @@
         <v>11</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="C37" s="42"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="42"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="42"/>
-      <c r="I37" s="42"/>
-      <c r="J37" s="42"/>
-      <c r="K37" s="42"/>
+        <v>575</v>
+      </c>
+      <c r="C37" s="80" t="s">
+        <v>576</v>
+      </c>
+      <c r="D37" s="80" t="s">
+        <v>577</v>
+      </c>
+      <c r="E37" s="80" t="s">
+        <v>576</v>
+      </c>
+      <c r="F37" s="80" t="s">
+        <v>578</v>
+      </c>
+      <c r="G37" s="80" t="s">
+        <v>579</v>
+      </c>
+      <c r="H37" s="80" t="s">
+        <v>580</v>
+      </c>
+      <c r="I37" s="81" t="s">
+        <v>581</v>
+      </c>
+      <c r="J37" s="81" t="s">
+        <v>582</v>
+      </c>
+      <c r="K37" s="80" t="s">
+        <v>502</v>
+      </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
-      <c r="AB37" s="1"/>
-      <c r="AC37" s="1"/>
-      <c r="AD37" s="1"/>
+      <c r="O37" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="P37" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q37" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y37" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="57" t="n">
+        <v>219</v>
+      </c>
+      <c r="AA37" s="57" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB37" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="AE37" s="1"/>
       <c r="AF37" s="1"/>
       <c r="AG37" s="1"/>
@@ -10081,36 +11149,86 @@
         <v>12</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38" s="42"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="42"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="42"/>
-      <c r="J38" s="42"/>
-      <c r="K38" s="42"/>
+        <v>583</v>
+      </c>
+      <c r="C38" s="80" t="s">
+        <v>584</v>
+      </c>
+      <c r="D38" s="80" t="s">
+        <v>585</v>
+      </c>
+      <c r="E38" s="80" t="s">
+        <v>584</v>
+      </c>
+      <c r="F38" s="80" t="s">
+        <v>586</v>
+      </c>
+      <c r="G38" s="80" t="s">
+        <v>587</v>
+      </c>
+      <c r="H38" s="80" t="s">
+        <v>588</v>
+      </c>
+      <c r="I38" s="81" t="s">
+        <v>589</v>
+      </c>
+      <c r="J38" s="81" t="s">
+        <v>590</v>
+      </c>
+      <c r="K38" s="80" t="s">
+        <v>502</v>
+      </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
-      <c r="AB38" s="1"/>
-      <c r="AC38" s="1"/>
-      <c r="AD38" s="1"/>
+      <c r="O38" s="54" t="n">
+        <v>11</v>
+      </c>
+      <c r="P38" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q38" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="57" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA38" s="57" t="n">
+        <v>49</v>
+      </c>
+      <c r="AB38" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="AE38" s="1"/>
       <c r="AF38" s="1"/>
       <c r="AG38" s="1"/>
@@ -10128,54 +11246,86 @@
         <v>13</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" s="42" t="s">
-        <v>523</v>
-      </c>
-      <c r="D39" s="42" t="s">
-        <v>524</v>
-      </c>
-      <c r="E39" s="42" t="s">
-        <v>523</v>
-      </c>
-      <c r="F39" s="42" t="s">
-        <v>525</v>
-      </c>
-      <c r="G39" s="42" t="s">
-        <v>526</v>
-      </c>
-      <c r="H39" s="42" t="s">
-        <v>527</v>
-      </c>
-      <c r="I39" s="42" t="s">
-        <v>528</v>
-      </c>
-      <c r="J39" s="42" t="s">
-        <v>529</v>
-      </c>
-      <c r="K39" s="42" t="s">
-        <v>501</v>
+        <v>591</v>
+      </c>
+      <c r="C39" s="80" t="s">
+        <v>592</v>
+      </c>
+      <c r="D39" s="80" t="s">
+        <v>593</v>
+      </c>
+      <c r="E39" s="80" t="s">
+        <v>592</v>
+      </c>
+      <c r="F39" s="80" t="s">
+        <v>594</v>
+      </c>
+      <c r="G39" s="80" t="s">
+        <v>595</v>
+      </c>
+      <c r="H39" s="80" t="s">
+        <v>596</v>
+      </c>
+      <c r="I39" s="81" t="s">
+        <v>597</v>
+      </c>
+      <c r="J39" s="81" t="s">
+        <v>598</v>
+      </c>
+      <c r="K39" s="80" t="s">
+        <v>502</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
-      <c r="AB39" s="1"/>
-      <c r="AC39" s="1"/>
-      <c r="AD39" s="1"/>
+      <c r="O39" s="54" t="n">
+        <v>12</v>
+      </c>
+      <c r="P39" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q39" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC39" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
       <c r="AG39" s="1"/>
@@ -10193,36 +11343,86 @@
         <v>14</v>
       </c>
       <c r="B40" s="56" t="s">
-        <v>115</v>
-      </c>
-      <c r="C40" s="42"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="42"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="42"/>
-      <c r="J40" s="42"/>
-      <c r="K40" s="42"/>
+        <v>599</v>
+      </c>
+      <c r="C40" s="80" t="s">
+        <v>600</v>
+      </c>
+      <c r="D40" s="80" t="s">
+        <v>601</v>
+      </c>
+      <c r="E40" s="80" t="s">
+        <v>600</v>
+      </c>
+      <c r="F40" s="80" t="s">
+        <v>602</v>
+      </c>
+      <c r="G40" s="80" t="s">
+        <v>603</v>
+      </c>
+      <c r="H40" s="80" t="s">
+        <v>604</v>
+      </c>
+      <c r="I40" s="81" t="s">
+        <v>605</v>
+      </c>
+      <c r="J40" s="81" t="s">
+        <v>606</v>
+      </c>
+      <c r="K40" s="80" t="s">
+        <v>502</v>
+      </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
-      <c r="R40" s="1"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="1"/>
-      <c r="X40" s="1"/>
-      <c r="Y40" s="1"/>
-      <c r="Z40" s="1"/>
-      <c r="AA40" s="1"/>
-      <c r="AB40" s="1"/>
-      <c r="AC40" s="1"/>
-      <c r="AD40" s="1"/>
+      <c r="O40" s="54" t="n">
+        <v>13</v>
+      </c>
+      <c r="P40" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD40" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="AE40" s="1"/>
       <c r="AF40" s="1"/>
       <c r="AG40" s="1"/>
@@ -10240,36 +11440,86 @@
         <v>15</v>
       </c>
       <c r="B41" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="42"/>
-      <c r="G41" s="42"/>
-      <c r="H41" s="42"/>
-      <c r="I41" s="42"/>
-      <c r="J41" s="42"/>
-      <c r="K41" s="42"/>
+        <v>607</v>
+      </c>
+      <c r="C41" s="80" t="s">
+        <v>608</v>
+      </c>
+      <c r="D41" s="80" t="s">
+        <v>609</v>
+      </c>
+      <c r="E41" s="80" t="s">
+        <v>608</v>
+      </c>
+      <c r="F41" s="80" t="s">
+        <v>610</v>
+      </c>
+      <c r="G41" s="80" t="s">
+        <v>611</v>
+      </c>
+      <c r="H41" s="80" t="s">
+        <v>612</v>
+      </c>
+      <c r="I41" s="81" t="s">
+        <v>613</v>
+      </c>
+      <c r="J41" s="81" t="s">
+        <v>614</v>
+      </c>
+      <c r="K41" s="80" t="s">
+        <v>502</v>
+      </c>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
-      <c r="W41" s="1"/>
-      <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
-      <c r="Z41" s="1"/>
-      <c r="AA41" s="1"/>
-      <c r="AB41" s="1"/>
-      <c r="AC41" s="1"/>
-      <c r="AD41" s="1"/>
+      <c r="O41" s="54" t="n">
+        <v>14</v>
+      </c>
+      <c r="P41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="57" t="n">
+        <v>2</v>
+      </c>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
       <c r="AG41" s="1"/>
@@ -10457,260 +11707,824 @@
       <c r="K59" s="55" t="s">
         <v>101</v>
       </c>
+      <c r="P59" s="82" t="n">
+        <v>829</v>
+      </c>
+      <c r="Q59" s="82" t="n">
+        <v>842</v>
+      </c>
+      <c r="R59" s="82" t="n">
+        <v>24</v>
+      </c>
+      <c r="S59" s="82" t="n">
+        <v>983</v>
+      </c>
+      <c r="T59" s="82" t="n">
+        <v>984</v>
+      </c>
+      <c r="U59" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="83"/>
     </row>
     <row r="60" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="56" t="n">
         <v>1</v>
       </c>
       <c r="B60" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="J60" s="42"/>
-      <c r="K60" s="42"/>
+        <v>494</v>
+      </c>
+      <c r="C60" s="42" t="s">
+        <v>615</v>
+      </c>
+      <c r="D60" s="42" t="s">
+        <v>616</v>
+      </c>
+      <c r="E60" s="42" t="s">
+        <v>615</v>
+      </c>
+      <c r="F60" s="42" t="s">
+        <v>617</v>
+      </c>
+      <c r="G60" s="42" t="s">
+        <v>618</v>
+      </c>
+      <c r="H60" s="42" t="s">
+        <v>619</v>
+      </c>
+      <c r="I60" s="84" t="s">
+        <v>620</v>
+      </c>
+      <c r="J60" s="84" t="s">
+        <v>621</v>
+      </c>
+      <c r="K60" s="42" t="s">
+        <v>622</v>
+      </c>
+      <c r="P60" s="82" t="n">
+        <v>523</v>
+      </c>
+      <c r="Q60" s="82" t="n">
+        <v>531</v>
+      </c>
+      <c r="R60" s="82" t="n">
+        <v>30</v>
+      </c>
+      <c r="S60" s="82" t="n">
+        <v>913</v>
+      </c>
+      <c r="T60" s="82" t="n">
+        <v>913</v>
+      </c>
+      <c r="U60" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="V60" s="83"/>
     </row>
     <row r="61" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="56" t="n">
         <v>2</v>
       </c>
       <c r="B61" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="J61" s="42"/>
-      <c r="K61" s="42"/>
+        <v>503</v>
+      </c>
+      <c r="C61" s="42" t="s">
+        <v>623</v>
+      </c>
+      <c r="D61" s="42" t="s">
+        <v>624</v>
+      </c>
+      <c r="E61" s="42" t="s">
+        <v>623</v>
+      </c>
+      <c r="F61" s="42" t="s">
+        <v>625</v>
+      </c>
+      <c r="G61" s="42" t="s">
+        <v>626</v>
+      </c>
+      <c r="H61" s="42" t="s">
+        <v>627</v>
+      </c>
+      <c r="I61" s="84" t="s">
+        <v>628</v>
+      </c>
+      <c r="J61" s="84" t="s">
+        <v>629</v>
+      </c>
+      <c r="K61" s="42" t="s">
+        <v>630</v>
+      </c>
+      <c r="P61" s="82" t="n">
+        <v>723</v>
+      </c>
+      <c r="Q61" s="82" t="n">
+        <v>697</v>
+      </c>
+      <c r="R61" s="82" t="n">
+        <v>4</v>
+      </c>
+      <c r="S61" s="82" t="n">
+        <v>956</v>
+      </c>
+      <c r="T61" s="82" t="n">
+        <v>957</v>
+      </c>
+      <c r="U61" s="82" t="n">
+        <v>3</v>
+      </c>
+      <c r="V61" s="83"/>
     </row>
     <row r="62" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="56" t="n">
         <v>4</v>
       </c>
       <c r="B62" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="J62" s="42"/>
-      <c r="K62" s="42"/>
+        <v>511</v>
+      </c>
+      <c r="C62" s="42" t="s">
+        <v>631</v>
+      </c>
+      <c r="D62" s="42" t="s">
+        <v>632</v>
+      </c>
+      <c r="E62" s="42" t="s">
+        <v>631</v>
+      </c>
+      <c r="F62" s="42" t="s">
+        <v>633</v>
+      </c>
+      <c r="G62" s="42" t="s">
+        <v>634</v>
+      </c>
+      <c r="H62" s="42" t="s">
+        <v>635</v>
+      </c>
+      <c r="I62" s="84" t="s">
+        <v>636</v>
+      </c>
+      <c r="J62" s="84" t="s">
+        <v>637</v>
+      </c>
+      <c r="K62" s="42" t="s">
+        <v>638</v>
+      </c>
+      <c r="P62" s="82" t="n">
+        <v>583</v>
+      </c>
+      <c r="Q62" s="82" t="n">
+        <v>585</v>
+      </c>
+      <c r="R62" s="82" t="n">
+        <v>5</v>
+      </c>
+      <c r="S62" s="82" t="n">
+        <v>886</v>
+      </c>
+      <c r="T62" s="82" t="n">
+        <v>887</v>
+      </c>
+      <c r="U62" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="V62" s="83"/>
     </row>
     <row r="63" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="56" t="n">
         <v>5</v>
       </c>
       <c r="B63" s="56" t="s">
-        <v>105</v>
+        <v>519</v>
       </c>
       <c r="C63" s="42" t="s">
-        <v>530</v>
+        <v>639</v>
       </c>
       <c r="D63" s="42" t="s">
-        <v>531</v>
+        <v>640</v>
       </c>
       <c r="E63" s="42" t="s">
-        <v>530</v>
+        <v>639</v>
       </c>
       <c r="F63" s="42" t="s">
-        <v>532</v>
+        <v>641</v>
       </c>
       <c r="G63" s="42" t="s">
-        <v>533</v>
+        <v>642</v>
       </c>
       <c r="H63" s="42" t="s">
-        <v>534</v>
-      </c>
-      <c r="I63" s="42" t="s">
-        <v>535</v>
-      </c>
-      <c r="J63" s="42" t="s">
-        <v>536</v>
+        <v>643</v>
+      </c>
+      <c r="I63" s="84" t="s">
+        <v>644</v>
+      </c>
+      <c r="J63" s="84" t="s">
+        <v>645</v>
       </c>
       <c r="K63" s="42" t="s">
-        <v>537</v>
-      </c>
+        <v>646</v>
+      </c>
+      <c r="P63" s="82" t="n">
+        <v>416</v>
+      </c>
+      <c r="Q63" s="82" t="n">
+        <v>423</v>
+      </c>
+      <c r="R63" s="82" t="n">
+        <v>12</v>
+      </c>
+      <c r="S63" s="82" t="n">
+        <v>659</v>
+      </c>
+      <c r="T63" s="82" t="n">
+        <v>677</v>
+      </c>
+      <c r="U63" s="82" t="n">
+        <v>23</v>
+      </c>
+      <c r="V63" s="83"/>
     </row>
     <row r="64" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="56" t="n">
         <v>6</v>
       </c>
       <c r="B64" s="56" t="s">
-        <v>106</v>
-      </c>
-      <c r="J64" s="42"/>
-      <c r="K64" s="42"/>
+        <v>527</v>
+      </c>
+      <c r="C64" s="42" t="s">
+        <v>647</v>
+      </c>
+      <c r="D64" s="42" t="s">
+        <v>648</v>
+      </c>
+      <c r="E64" s="42" t="s">
+        <v>647</v>
+      </c>
+      <c r="F64" s="42" t="s">
+        <v>649</v>
+      </c>
+      <c r="G64" s="42" t="s">
+        <v>650</v>
+      </c>
+      <c r="H64" s="42" t="s">
+        <v>651</v>
+      </c>
+      <c r="I64" s="84" t="s">
+        <v>652</v>
+      </c>
+      <c r="J64" s="84" t="s">
+        <v>653</v>
+      </c>
+      <c r="K64" s="42" t="s">
+        <v>654</v>
+      </c>
+      <c r="P64" s="82" t="n">
+        <v>560</v>
+      </c>
+      <c r="Q64" s="82" t="n">
+        <v>583</v>
+      </c>
+      <c r="R64" s="82" t="n">
+        <v>22</v>
+      </c>
+      <c r="S64" s="82" t="n">
+        <v>828</v>
+      </c>
+      <c r="T64" s="82" t="n">
+        <v>823</v>
+      </c>
+      <c r="U64" s="82" t="n">
+        <v>19</v>
+      </c>
+      <c r="V64" s="83"/>
     </row>
     <row r="65" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="56" t="n">
         <v>8</v>
       </c>
       <c r="B65" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="J65" s="42"/>
-      <c r="K65" s="42"/>
+        <v>535</v>
+      </c>
+      <c r="C65" s="42" t="s">
+        <v>655</v>
+      </c>
+      <c r="D65" s="42" t="s">
+        <v>656</v>
+      </c>
+      <c r="E65" s="42" t="s">
+        <v>655</v>
+      </c>
+      <c r="F65" s="42" t="s">
+        <v>657</v>
+      </c>
+      <c r="G65" s="42" t="s">
+        <v>658</v>
+      </c>
+      <c r="H65" s="42" t="s">
+        <v>659</v>
+      </c>
+      <c r="I65" s="84" t="s">
+        <v>660</v>
+      </c>
+      <c r="J65" s="84" t="s">
+        <v>661</v>
+      </c>
+      <c r="K65" s="42" t="s">
+        <v>662</v>
+      </c>
+      <c r="P65" s="82" t="n">
+        <v>281</v>
+      </c>
+      <c r="Q65" s="82" t="n">
+        <v>303</v>
+      </c>
+      <c r="R65" s="82" t="n">
+        <v>24</v>
+      </c>
+      <c r="S65" s="82" t="n">
+        <v>330</v>
+      </c>
+      <c r="T65" s="82" t="n">
+        <v>357</v>
+      </c>
+      <c r="U65" s="82" t="n">
+        <v>24</v>
+      </c>
+      <c r="V65" s="83"/>
     </row>
     <row r="66" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="56" t="n">
         <v>9</v>
       </c>
       <c r="B66" s="56" t="s">
-        <v>108</v>
+        <v>543</v>
       </c>
       <c r="C66" s="42" t="s">
-        <v>538</v>
+        <v>663</v>
       </c>
       <c r="D66" s="42" t="s">
-        <v>539</v>
+        <v>664</v>
       </c>
       <c r="E66" s="42" t="s">
-        <v>538</v>
+        <v>663</v>
       </c>
       <c r="F66" s="42" t="s">
-        <v>540</v>
+        <v>665</v>
       </c>
       <c r="G66" s="42" t="s">
-        <v>541</v>
+        <v>666</v>
       </c>
       <c r="H66" s="42" t="s">
-        <v>542</v>
-      </c>
-      <c r="I66" s="42" t="s">
-        <v>543</v>
-      </c>
-      <c r="J66" s="42" t="s">
-        <v>544</v>
+        <v>667</v>
+      </c>
+      <c r="I66" s="84" t="s">
+        <v>668</v>
+      </c>
+      <c r="J66" s="84" t="s">
+        <v>669</v>
       </c>
       <c r="K66" s="42" t="s">
-        <v>545</v>
-      </c>
+        <v>670</v>
+      </c>
+      <c r="P66" s="82" t="n">
+        <v>209</v>
+      </c>
+      <c r="Q66" s="82" t="n">
+        <v>230</v>
+      </c>
+      <c r="R66" s="82" t="n">
+        <v>41</v>
+      </c>
+      <c r="S66" s="82" t="n">
+        <v>239</v>
+      </c>
+      <c r="T66" s="82" t="n">
+        <v>246</v>
+      </c>
+      <c r="U66" s="82" t="n">
+        <v>46</v>
+      </c>
+      <c r="V66" s="83"/>
     </row>
     <row r="67" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="56" t="n">
         <v>10</v>
       </c>
       <c r="B67" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="J67" s="42"/>
-      <c r="K67" s="42"/>
+        <v>551</v>
+      </c>
+      <c r="C67" s="42" t="s">
+        <v>671</v>
+      </c>
+      <c r="D67" s="42" t="s">
+        <v>672</v>
+      </c>
+      <c r="E67" s="42" t="s">
+        <v>671</v>
+      </c>
+      <c r="F67" s="42" t="s">
+        <v>673</v>
+      </c>
+      <c r="G67" s="42" t="s">
+        <v>674</v>
+      </c>
+      <c r="H67" s="42" t="s">
+        <v>675</v>
+      </c>
+      <c r="I67" s="84" t="s">
+        <v>676</v>
+      </c>
+      <c r="J67" s="84" t="s">
+        <v>677</v>
+      </c>
+      <c r="K67" s="42" t="s">
+        <v>678</v>
+      </c>
+      <c r="P67" s="82" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q67" s="82" t="n">
+        <v>208</v>
+      </c>
+      <c r="R67" s="82" t="n">
+        <v>31</v>
+      </c>
+      <c r="S67" s="82" t="n">
+        <v>223</v>
+      </c>
+      <c r="T67" s="82" t="n">
+        <v>245</v>
+      </c>
+      <c r="U67" s="82" t="n">
+        <v>44</v>
+      </c>
+      <c r="V67" s="83"/>
     </row>
     <row r="68" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="n">
         <v>12</v>
       </c>
       <c r="B68" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="J68" s="42"/>
-      <c r="K68" s="42"/>
+        <v>559</v>
+      </c>
+      <c r="C68" s="42" t="s">
+        <v>679</v>
+      </c>
+      <c r="D68" s="42" t="s">
+        <v>680</v>
+      </c>
+      <c r="E68" s="42" t="s">
+        <v>679</v>
+      </c>
+      <c r="F68" s="42" t="s">
+        <v>681</v>
+      </c>
+      <c r="G68" s="42" t="s">
+        <v>682</v>
+      </c>
+      <c r="H68" s="42" t="s">
+        <v>683</v>
+      </c>
+      <c r="I68" s="84" t="s">
+        <v>684</v>
+      </c>
+      <c r="J68" s="84" t="s">
+        <v>685</v>
+      </c>
+      <c r="K68" s="42" t="s">
+        <v>686</v>
+      </c>
+      <c r="P68" s="82" t="n">
+        <v>587</v>
+      </c>
+      <c r="Q68" s="82" t="n">
+        <v>595</v>
+      </c>
+      <c r="R68" s="82" t="n">
+        <v>7</v>
+      </c>
+      <c r="S68" s="82" t="n">
+        <v>890</v>
+      </c>
+      <c r="T68" s="82" t="n">
+        <v>892</v>
+      </c>
+      <c r="U68" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="V68" s="83"/>
     </row>
     <row r="69" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="56" t="n">
         <v>13</v>
       </c>
       <c r="B69" s="56" t="s">
-        <v>111</v>
+        <v>567</v>
       </c>
       <c r="C69" s="42" t="s">
-        <v>546</v>
+        <v>687</v>
       </c>
       <c r="D69" s="42" t="s">
-        <v>547</v>
+        <v>688</v>
       </c>
       <c r="E69" s="42" t="s">
-        <v>546</v>
+        <v>687</v>
       </c>
       <c r="F69" s="42" t="s">
-        <v>548</v>
+        <v>689</v>
       </c>
       <c r="G69" s="42" t="s">
-        <v>549</v>
+        <v>690</v>
       </c>
       <c r="H69" s="42" t="s">
-        <v>550</v>
-      </c>
-      <c r="I69" s="42" t="s">
-        <v>551</v>
-      </c>
-      <c r="J69" s="42" t="s">
-        <v>552</v>
+        <v>691</v>
+      </c>
+      <c r="I69" s="84" t="s">
+        <v>692</v>
+      </c>
+      <c r="J69" s="84" t="s">
+        <v>693</v>
       </c>
       <c r="K69" s="42" t="s">
-        <v>553</v>
-      </c>
+        <v>694</v>
+      </c>
+      <c r="P69" s="82" t="n">
+        <v>416</v>
+      </c>
+      <c r="Q69" s="82" t="n">
+        <v>412</v>
+      </c>
+      <c r="R69" s="82" t="n">
+        <v>18</v>
+      </c>
+      <c r="S69" s="82" t="n">
+        <v>672</v>
+      </c>
+      <c r="T69" s="82" t="n">
+        <v>689</v>
+      </c>
+      <c r="U69" s="82" t="n">
+        <v>27</v>
+      </c>
+      <c r="V69" s="83"/>
     </row>
     <row r="70" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
         <v>14</v>
       </c>
       <c r="B70" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="J70" s="42"/>
-      <c r="K70" s="42"/>
+        <v>575</v>
+      </c>
+      <c r="C70" s="42" t="s">
+        <v>695</v>
+      </c>
+      <c r="D70" s="42" t="s">
+        <v>696</v>
+      </c>
+      <c r="E70" s="42" t="s">
+        <v>695</v>
+      </c>
+      <c r="F70" s="42" t="s">
+        <v>697</v>
+      </c>
+      <c r="G70" s="42" t="s">
+        <v>698</v>
+      </c>
+      <c r="H70" s="42" t="s">
+        <v>699</v>
+      </c>
+      <c r="I70" s="84" t="s">
+        <v>700</v>
+      </c>
+      <c r="J70" s="84" t="s">
+        <v>701</v>
+      </c>
+      <c r="K70" s="42" t="s">
+        <v>702</v>
+      </c>
+      <c r="P70" s="82" t="n">
+        <v>561</v>
+      </c>
+      <c r="Q70" s="82" t="n">
+        <v>539</v>
+      </c>
+      <c r="R70" s="82" t="n">
+        <v>26</v>
+      </c>
+      <c r="S70" s="82" t="n">
+        <v>836</v>
+      </c>
+      <c r="T70" s="82" t="n">
+        <v>847</v>
+      </c>
+      <c r="U70" s="82" t="n">
+        <v>15</v>
+      </c>
+      <c r="V70" s="83"/>
     </row>
     <row r="71" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="56" t="n">
         <v>16</v>
       </c>
       <c r="B71" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="J71" s="42"/>
-      <c r="K71" s="42"/>
+        <v>583</v>
+      </c>
+      <c r="C71" s="42" t="s">
+        <v>703</v>
+      </c>
+      <c r="D71" s="42" t="s">
+        <v>704</v>
+      </c>
+      <c r="E71" s="42" t="s">
+        <v>703</v>
+      </c>
+      <c r="F71" s="42" t="s">
+        <v>705</v>
+      </c>
+      <c r="G71" s="42" t="s">
+        <v>706</v>
+      </c>
+      <c r="H71" s="42" t="s">
+        <v>707</v>
+      </c>
+      <c r="I71" s="84" t="s">
+        <v>708</v>
+      </c>
+      <c r="J71" s="84" t="s">
+        <v>709</v>
+      </c>
+      <c r="K71" s="42" t="s">
+        <v>710</v>
+      </c>
+      <c r="P71" s="82" t="n">
+        <v>297</v>
+      </c>
+      <c r="Q71" s="82" t="n">
+        <v>314</v>
+      </c>
+      <c r="R71" s="82" t="n">
+        <v>26</v>
+      </c>
+      <c r="S71" s="82" t="n">
+        <v>343</v>
+      </c>
+      <c r="T71" s="82" t="n">
+        <v>359</v>
+      </c>
+      <c r="U71" s="82" t="n">
+        <v>29</v>
+      </c>
+      <c r="V71" s="83"/>
     </row>
     <row r="72" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
         <v>17</v>
       </c>
       <c r="B72" s="56" t="s">
-        <v>114</v>
+        <v>591</v>
       </c>
       <c r="C72" s="42" t="s">
-        <v>554</v>
+        <v>711</v>
       </c>
       <c r="D72" s="42" t="s">
-        <v>555</v>
+        <v>712</v>
       </c>
       <c r="E72" s="42" t="s">
-        <v>554</v>
+        <v>711</v>
       </c>
       <c r="F72" s="42" t="s">
-        <v>556</v>
+        <v>713</v>
       </c>
       <c r="G72" s="42" t="s">
-        <v>557</v>
+        <v>714</v>
       </c>
       <c r="H72" s="42" t="s">
-        <v>558</v>
-      </c>
-      <c r="I72" s="42" t="s">
-        <v>559</v>
-      </c>
-      <c r="J72" s="42" t="s">
-        <v>560</v>
+        <v>715</v>
+      </c>
+      <c r="I72" s="84" t="s">
+        <v>716</v>
+      </c>
+      <c r="J72" s="84" t="s">
+        <v>717</v>
       </c>
       <c r="K72" s="42" t="s">
-        <v>561</v>
-      </c>
+        <v>718</v>
+      </c>
+      <c r="P72" s="82" t="n">
+        <v>223</v>
+      </c>
+      <c r="Q72" s="82" t="n">
+        <v>247</v>
+      </c>
+      <c r="R72" s="82" t="n">
+        <v>46</v>
+      </c>
+      <c r="S72" s="82" t="n">
+        <v>214</v>
+      </c>
+      <c r="T72" s="82" t="n">
+        <v>245</v>
+      </c>
+      <c r="U72" s="82" t="n">
+        <v>35</v>
+      </c>
+      <c r="V72" s="83"/>
     </row>
     <row r="73" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="56" t="n">
         <v>18</v>
       </c>
       <c r="B73" s="56" t="s">
-        <v>115</v>
-      </c>
-      <c r="J73" s="42"/>
-      <c r="K73" s="42"/>
+        <v>599</v>
+      </c>
+      <c r="C73" s="42" t="s">
+        <v>719</v>
+      </c>
+      <c r="D73" s="42" t="s">
+        <v>720</v>
+      </c>
+      <c r="E73" s="42" t="s">
+        <v>719</v>
+      </c>
+      <c r="F73" s="42" t="s">
+        <v>721</v>
+      </c>
+      <c r="G73" s="42" t="s">
+        <v>722</v>
+      </c>
+      <c r="H73" s="42" t="s">
+        <v>723</v>
+      </c>
+      <c r="I73" s="84" t="s">
+        <v>724</v>
+      </c>
+      <c r="J73" s="84" t="s">
+        <v>725</v>
+      </c>
+      <c r="K73" s="42" t="s">
+        <v>726</v>
+      </c>
+      <c r="P73" s="82" t="n">
+        <v>205</v>
+      </c>
+      <c r="Q73" s="82" t="n">
+        <v>230</v>
+      </c>
+      <c r="R73" s="82" t="n">
+        <v>46</v>
+      </c>
+      <c r="S73" s="82" t="n">
+        <v>224</v>
+      </c>
+      <c r="T73" s="82" t="n">
+        <v>260</v>
+      </c>
+      <c r="U73" s="82" t="n">
+        <v>47</v>
+      </c>
+      <c r="V73" s="83"/>
     </row>
     <row r="74" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="56" t="n">
         <v>20</v>
       </c>
       <c r="B74" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="J74" s="42"/>
-      <c r="K74" s="42"/>
+        <v>607</v>
+      </c>
+      <c r="C74" s="42" t="s">
+        <v>727</v>
+      </c>
+      <c r="D74" s="42" t="s">
+        <v>728</v>
+      </c>
+      <c r="E74" s="42" t="s">
+        <v>727</v>
+      </c>
+      <c r="F74" s="42" t="s">
+        <v>729</v>
+      </c>
+      <c r="G74" s="42" t="s">
+        <v>730</v>
+      </c>
+      <c r="H74" s="42" t="s">
+        <v>731</v>
+      </c>
+      <c r="I74" s="84" t="s">
+        <v>732</v>
+      </c>
+      <c r="J74" s="84" t="s">
+        <v>733</v>
+      </c>
+      <c r="K74" s="42" t="s">
+        <v>734</v>
+      </c>
+      <c r="P74" s="85"/>
+      <c r="Q74" s="85"/>
+      <c r="R74" s="85"/>
+      <c r="S74" s="85"/>
     </row>
     <row r="82" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="35" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="B82" s="35"/>
       <c r="C82" s="35"/>
@@ -10739,22 +12553,22 @@
     </row>
     <row r="84" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="60" t="s">
-        <v>563</v>
+        <v>736</v>
       </c>
       <c r="B84" s="42" t="s">
-        <v>564</v>
+        <v>737</v>
       </c>
       <c r="C84" s="42" t="s">
-        <v>565</v>
+        <v>738</v>
       </c>
       <c r="D84" s="42" t="s">
-        <v>566</v>
+        <v>739</v>
       </c>
       <c r="E84" s="42" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="F84" s="42" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10762,199 +12576,199 @@
         <v>134</v>
       </c>
       <c r="B85" s="42" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="C85" s="42" t="s">
-        <v>570</v>
+        <v>743</v>
       </c>
       <c r="D85" s="42" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="E85" s="42" t="s">
-        <v>572</v>
+        <v>745</v>
       </c>
       <c r="F85" s="42" t="s">
-        <v>573</v>
+        <v>746</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="60" t="s">
-        <v>574</v>
+        <v>747</v>
       </c>
       <c r="B86" s="42" t="s">
-        <v>575</v>
+        <v>748</v>
       </c>
       <c r="C86" s="42" t="s">
-        <v>576</v>
+        <v>749</v>
       </c>
       <c r="D86" s="42" t="s">
-        <v>577</v>
+        <v>750</v>
       </c>
       <c r="E86" s="42" t="s">
-        <v>578</v>
+        <v>751</v>
       </c>
       <c r="F86" s="42" t="s">
-        <v>579</v>
+        <v>752</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="60" t="s">
-        <v>580</v>
+        <v>753</v>
       </c>
       <c r="B87" s="42" t="s">
-        <v>581</v>
+        <v>754</v>
       </c>
       <c r="C87" s="42" t="s">
-        <v>582</v>
+        <v>755</v>
       </c>
       <c r="D87" s="42" t="s">
-        <v>583</v>
+        <v>756</v>
       </c>
       <c r="E87" s="42" t="s">
-        <v>584</v>
+        <v>757</v>
       </c>
       <c r="F87" s="42" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="60" t="s">
-        <v>586</v>
+        <v>759</v>
       </c>
       <c r="B88" s="42" t="s">
-        <v>587</v>
+        <v>760</v>
       </c>
       <c r="C88" s="42" t="s">
-        <v>588</v>
+        <v>761</v>
       </c>
       <c r="D88" s="42" t="s">
-        <v>589</v>
+        <v>762</v>
       </c>
       <c r="E88" s="42" t="s">
-        <v>590</v>
+        <v>763</v>
       </c>
       <c r="F88" s="42" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="60" t="s">
-        <v>592</v>
+        <v>765</v>
       </c>
       <c r="B89" s="42" t="s">
-        <v>593</v>
+        <v>766</v>
       </c>
       <c r="C89" s="42" t="s">
-        <v>594</v>
+        <v>767</v>
       </c>
       <c r="D89" s="42" t="s">
-        <v>595</v>
+        <v>768</v>
       </c>
       <c r="E89" s="42" t="s">
-        <v>596</v>
+        <v>769</v>
       </c>
       <c r="F89" s="42" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="60" t="s">
-        <v>598</v>
+        <v>771</v>
       </c>
       <c r="B90" s="42" t="s">
-        <v>599</v>
+        <v>772</v>
       </c>
       <c r="C90" s="42" t="s">
-        <v>600</v>
+        <v>773</v>
       </c>
       <c r="D90" s="42" t="s">
-        <v>601</v>
+        <v>774</v>
       </c>
       <c r="E90" s="42" t="s">
-        <v>602</v>
+        <v>775</v>
       </c>
       <c r="F90" s="42" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="60" t="s">
-        <v>604</v>
+        <v>777</v>
       </c>
       <c r="B91" s="42" t="s">
-        <v>605</v>
+        <v>778</v>
       </c>
       <c r="C91" s="42" t="s">
-        <v>606</v>
+        <v>779</v>
       </c>
       <c r="D91" s="42" t="s">
-        <v>607</v>
+        <v>780</v>
       </c>
       <c r="E91" s="42" t="s">
-        <v>608</v>
+        <v>781</v>
       </c>
       <c r="F91" s="42" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="60" t="s">
-        <v>610</v>
+        <v>783</v>
       </c>
       <c r="B92" s="42" t="s">
-        <v>611</v>
+        <v>784</v>
       </c>
       <c r="C92" s="42" t="s">
-        <v>612</v>
+        <v>785</v>
       </c>
       <c r="D92" s="42" t="s">
-        <v>613</v>
+        <v>786</v>
       </c>
       <c r="E92" s="42" t="s">
-        <v>614</v>
+        <v>787</v>
       </c>
       <c r="F92" s="42" t="s">
-        <v>615</v>
+        <v>788</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="60" t="s">
-        <v>616</v>
+        <v>789</v>
       </c>
       <c r="B93" s="42" t="s">
-        <v>617</v>
+        <v>790</v>
       </c>
       <c r="C93" s="42" t="s">
-        <v>618</v>
+        <v>791</v>
       </c>
       <c r="D93" s="42" t="s">
-        <v>619</v>
+        <v>792</v>
       </c>
       <c r="E93" s="42" t="s">
-        <v>620</v>
+        <v>793</v>
       </c>
       <c r="F93" s="42" t="s">
-        <v>621</v>
+        <v>794</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="60" t="s">
-        <v>622</v>
+        <v>795</v>
       </c>
       <c r="B94" s="42" t="s">
-        <v>623</v>
+        <v>796</v>
       </c>
       <c r="C94" s="42" t="s">
-        <v>624</v>
+        <v>797</v>
       </c>
       <c r="D94" s="42" t="s">
-        <v>625</v>
+        <v>798</v>
       </c>
       <c r="E94" s="42" t="s">
-        <v>626</v>
+        <v>799</v>
       </c>
       <c r="F94" s="42" t="s">
-        <v>627</v>
+        <v>800</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10962,19 +12776,19 @@
         <v>224</v>
       </c>
       <c r="B95" s="42" t="s">
-        <v>628</v>
+        <v>801</v>
       </c>
       <c r="C95" s="42" t="s">
-        <v>629</v>
+        <v>802</v>
       </c>
       <c r="D95" s="42" t="s">
-        <v>630</v>
+        <v>803</v>
       </c>
       <c r="E95" s="42" t="s">
-        <v>631</v>
+        <v>804</v>
       </c>
       <c r="F95" s="42" t="s">
-        <v>632</v>
+        <v>805</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10982,19 +12796,19 @@
         <v>230</v>
       </c>
       <c r="B96" s="42" t="s">
-        <v>633</v>
+        <v>806</v>
       </c>
       <c r="C96" s="42" t="s">
-        <v>634</v>
+        <v>807</v>
       </c>
       <c r="D96" s="42" t="s">
-        <v>635</v>
+        <v>808</v>
       </c>
       <c r="E96" s="42" t="s">
-        <v>636</v>
+        <v>809</v>
       </c>
       <c r="F96" s="42" t="s">
-        <v>637</v>
+        <v>810</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11002,19 +12816,19 @@
         <v>236</v>
       </c>
       <c r="B97" s="42" t="s">
-        <v>638</v>
+        <v>811</v>
       </c>
       <c r="C97" s="42" t="s">
-        <v>639</v>
+        <v>812</v>
       </c>
       <c r="D97" s="42" t="s">
-        <v>640</v>
+        <v>813</v>
       </c>
       <c r="E97" s="42" t="s">
-        <v>641</v>
+        <v>814</v>
       </c>
       <c r="F97" s="42" t="s">
-        <v>642</v>
+        <v>815</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11022,19 +12836,19 @@
         <v>242</v>
       </c>
       <c r="B98" s="42" t="s">
-        <v>643</v>
+        <v>816</v>
       </c>
       <c r="C98" s="42" t="s">
-        <v>644</v>
+        <v>817</v>
       </c>
       <c r="D98" s="42" t="s">
-        <v>645</v>
+        <v>818</v>
       </c>
       <c r="E98" s="42" t="s">
-        <v>646</v>
+        <v>819</v>
       </c>
       <c r="F98" s="42" t="s">
-        <v>647</v>
+        <v>820</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11042,19 +12856,19 @@
         <v>254</v>
       </c>
       <c r="B99" s="42" t="s">
-        <v>648</v>
+        <v>821</v>
       </c>
       <c r="C99" s="42" t="s">
-        <v>649</v>
+        <v>822</v>
       </c>
       <c r="D99" s="42" t="s">
-        <v>650</v>
+        <v>823</v>
       </c>
       <c r="E99" s="42" t="s">
-        <v>651</v>
+        <v>824</v>
       </c>
       <c r="F99" s="42" t="s">
-        <v>652</v>
+        <v>825</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11062,19 +12876,19 @@
         <v>260</v>
       </c>
       <c r="B100" s="42" t="s">
-        <v>653</v>
+        <v>826</v>
       </c>
       <c r="C100" s="42" t="s">
-        <v>654</v>
+        <v>827</v>
       </c>
       <c r="D100" s="42" t="s">
-        <v>655</v>
+        <v>828</v>
       </c>
       <c r="E100" s="42" t="s">
-        <v>656</v>
+        <v>829</v>
       </c>
       <c r="F100" s="42" t="s">
-        <v>657</v>
+        <v>830</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11082,39 +12896,39 @@
         <v>272</v>
       </c>
       <c r="B101" s="42" t="s">
-        <v>658</v>
+        <v>831</v>
       </c>
       <c r="C101" s="42" t="s">
-        <v>659</v>
+        <v>832</v>
       </c>
       <c r="D101" s="42" t="s">
-        <v>660</v>
+        <v>833</v>
       </c>
       <c r="E101" s="42" t="s">
-        <v>661</v>
+        <v>834</v>
       </c>
       <c r="F101" s="42" t="s">
-        <v>662</v>
+        <v>835</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="60" t="s">
-        <v>663</v>
+        <v>836</v>
       </c>
       <c r="B102" s="42" t="s">
-        <v>664</v>
+        <v>837</v>
       </c>
       <c r="C102" s="42" t="s">
-        <v>665</v>
+        <v>838</v>
       </c>
       <c r="D102" s="42" t="s">
-        <v>666</v>
+        <v>839</v>
       </c>
       <c r="E102" s="42" t="s">
-        <v>667</v>
+        <v>840</v>
       </c>
       <c r="F102" s="42" t="s">
-        <v>668</v>
+        <v>841</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11122,19 +12936,19 @@
         <v>284</v>
       </c>
       <c r="B103" s="42" t="s">
-        <v>669</v>
+        <v>842</v>
       </c>
       <c r="C103" s="42" t="s">
-        <v>670</v>
+        <v>843</v>
       </c>
       <c r="D103" s="42" t="s">
-        <v>671</v>
+        <v>844</v>
       </c>
       <c r="E103" s="42" t="s">
-        <v>672</v>
+        <v>845</v>
       </c>
       <c r="F103" s="42" t="s">
-        <v>673</v>
+        <v>846</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11142,19 +12956,19 @@
         <v>290</v>
       </c>
       <c r="B104" s="42" t="s">
-        <v>674</v>
+        <v>847</v>
       </c>
       <c r="C104" s="42" t="s">
-        <v>675</v>
+        <v>848</v>
       </c>
       <c r="D104" s="42" t="s">
-        <v>676</v>
+        <v>849</v>
       </c>
       <c r="E104" s="42" t="s">
-        <v>677</v>
+        <v>850</v>
       </c>
       <c r="F104" s="42" t="s">
-        <v>678</v>
+        <v>851</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11162,19 +12976,19 @@
         <v>296</v>
       </c>
       <c r="B105" s="42" t="s">
-        <v>679</v>
+        <v>852</v>
       </c>
       <c r="C105" s="42" t="s">
-        <v>680</v>
+        <v>853</v>
       </c>
       <c r="D105" s="42" t="s">
-        <v>681</v>
+        <v>854</v>
       </c>
       <c r="E105" s="42" t="s">
-        <v>682</v>
+        <v>855</v>
       </c>
       <c r="F105" s="42" t="s">
-        <v>683</v>
+        <v>856</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11182,19 +12996,19 @@
         <v>302</v>
       </c>
       <c r="B106" s="42" t="s">
-        <v>684</v>
+        <v>857</v>
       </c>
       <c r="C106" s="42" t="s">
-        <v>685</v>
+        <v>858</v>
       </c>
       <c r="D106" s="42" t="s">
-        <v>686</v>
+        <v>859</v>
       </c>
       <c r="E106" s="42" t="s">
-        <v>687</v>
+        <v>860</v>
       </c>
       <c r="F106" s="42" t="s">
-        <v>688</v>
+        <v>861</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11202,379 +13016,379 @@
         <v>308</v>
       </c>
       <c r="B107" s="42" t="s">
-        <v>689</v>
+        <v>862</v>
       </c>
       <c r="C107" s="42" t="s">
-        <v>690</v>
+        <v>863</v>
       </c>
       <c r="D107" s="42" t="s">
-        <v>691</v>
+        <v>864</v>
       </c>
       <c r="E107" s="42" t="s">
-        <v>692</v>
+        <v>865</v>
       </c>
       <c r="F107" s="42" t="s">
-        <v>693</v>
+        <v>866</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="60" t="s">
-        <v>694</v>
+        <v>867</v>
       </c>
       <c r="B108" s="42" t="s">
-        <v>695</v>
+        <v>868</v>
       </c>
       <c r="C108" s="42" t="s">
-        <v>696</v>
+        <v>869</v>
       </c>
       <c r="D108" s="42" t="s">
-        <v>697</v>
+        <v>870</v>
       </c>
       <c r="E108" s="42" t="s">
-        <v>698</v>
+        <v>871</v>
       </c>
       <c r="F108" s="42" t="s">
-        <v>699</v>
+        <v>872</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="60" t="s">
-        <v>700</v>
+        <v>873</v>
       </c>
       <c r="B109" s="42" t="s">
-        <v>701</v>
+        <v>874</v>
       </c>
       <c r="C109" s="42" t="s">
-        <v>702</v>
+        <v>875</v>
       </c>
       <c r="D109" s="42" t="s">
-        <v>703</v>
+        <v>876</v>
       </c>
       <c r="E109" s="42" t="s">
-        <v>704</v>
+        <v>877</v>
       </c>
       <c r="F109" s="42" t="s">
-        <v>705</v>
+        <v>878</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="60" t="s">
-        <v>706</v>
+        <v>879</v>
       </c>
       <c r="B110" s="42" t="s">
-        <v>707</v>
+        <v>880</v>
       </c>
       <c r="C110" s="42" t="s">
-        <v>708</v>
+        <v>881</v>
       </c>
       <c r="D110" s="42" t="s">
-        <v>709</v>
+        <v>882</v>
       </c>
       <c r="E110" s="42" t="s">
-        <v>710</v>
+        <v>883</v>
       </c>
       <c r="F110" s="42" t="s">
-        <v>711</v>
+        <v>884</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="60" t="s">
-        <v>712</v>
+        <v>885</v>
       </c>
       <c r="B111" s="42" t="s">
-        <v>713</v>
+        <v>886</v>
       </c>
       <c r="C111" s="42" t="s">
-        <v>714</v>
+        <v>887</v>
       </c>
       <c r="D111" s="42" t="s">
-        <v>715</v>
+        <v>888</v>
       </c>
       <c r="E111" s="42" t="s">
-        <v>716</v>
+        <v>889</v>
       </c>
       <c r="F111" s="42" t="s">
-        <v>717</v>
+        <v>890</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="60" t="s">
-        <v>718</v>
+        <v>891</v>
       </c>
       <c r="B112" s="42" t="s">
-        <v>719</v>
+        <v>892</v>
       </c>
       <c r="C112" s="42" t="s">
-        <v>720</v>
+        <v>893</v>
       </c>
       <c r="D112" s="42" t="s">
-        <v>721</v>
+        <v>894</v>
       </c>
       <c r="E112" s="42" t="s">
-        <v>722</v>
+        <v>895</v>
       </c>
       <c r="F112" s="42" t="s">
-        <v>723</v>
+        <v>896</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="60" t="s">
-        <v>724</v>
+        <v>897</v>
       </c>
       <c r="B113" s="42" t="s">
-        <v>725</v>
+        <v>898</v>
       </c>
       <c r="C113" s="42" t="s">
-        <v>726</v>
+        <v>899</v>
       </c>
       <c r="D113" s="42" t="s">
-        <v>727</v>
+        <v>900</v>
       </c>
       <c r="E113" s="42" t="s">
-        <v>728</v>
+        <v>901</v>
       </c>
       <c r="F113" s="42" t="s">
-        <v>729</v>
+        <v>902</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="60" t="s">
-        <v>730</v>
+        <v>903</v>
       </c>
       <c r="B114" s="42" t="s">
-        <v>731</v>
+        <v>904</v>
       </c>
       <c r="C114" s="42" t="s">
-        <v>732</v>
+        <v>905</v>
       </c>
       <c r="D114" s="42" t="s">
-        <v>733</v>
+        <v>906</v>
       </c>
       <c r="E114" s="42" t="s">
-        <v>734</v>
+        <v>907</v>
       </c>
       <c r="F114" s="42" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="60" t="s">
-        <v>736</v>
+        <v>909</v>
       </c>
       <c r="B115" s="42" t="s">
-        <v>737</v>
+        <v>910</v>
       </c>
       <c r="C115" s="42" t="s">
-        <v>738</v>
+        <v>911</v>
       </c>
       <c r="D115" s="42" t="s">
-        <v>739</v>
+        <v>912</v>
       </c>
       <c r="E115" s="42" t="s">
-        <v>740</v>
+        <v>913</v>
       </c>
       <c r="F115" s="42" t="s">
-        <v>741</v>
+        <v>914</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="60" t="s">
-        <v>742</v>
+        <v>915</v>
       </c>
       <c r="B116" s="42" t="s">
-        <v>743</v>
+        <v>916</v>
       </c>
       <c r="C116" s="42" t="s">
-        <v>744</v>
+        <v>917</v>
       </c>
       <c r="D116" s="42" t="s">
-        <v>745</v>
+        <v>918</v>
       </c>
       <c r="E116" s="42" t="s">
-        <v>746</v>
+        <v>919</v>
       </c>
       <c r="F116" s="42" t="s">
-        <v>747</v>
+        <v>920</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="60" t="s">
-        <v>748</v>
+        <v>921</v>
       </c>
       <c r="B117" s="42" t="s">
-        <v>749</v>
+        <v>922</v>
       </c>
       <c r="C117" s="42" t="s">
-        <v>750</v>
+        <v>923</v>
       </c>
       <c r="D117" s="42" t="s">
-        <v>751</v>
+        <v>924</v>
       </c>
       <c r="E117" s="42" t="s">
-        <v>752</v>
+        <v>925</v>
       </c>
       <c r="F117" s="42" t="s">
-        <v>753</v>
+        <v>926</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="60" t="s">
-        <v>754</v>
+        <v>927</v>
       </c>
       <c r="B118" s="42" t="s">
-        <v>755</v>
+        <v>928</v>
       </c>
       <c r="C118" s="42" t="s">
-        <v>756</v>
+        <v>929</v>
       </c>
       <c r="D118" s="42" t="s">
-        <v>757</v>
+        <v>930</v>
       </c>
       <c r="E118" s="42" t="s">
-        <v>758</v>
+        <v>931</v>
       </c>
       <c r="F118" s="42" t="s">
-        <v>759</v>
+        <v>932</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="60" t="s">
-        <v>760</v>
+        <v>933</v>
       </c>
       <c r="B119" s="42" t="s">
-        <v>761</v>
+        <v>934</v>
       </c>
       <c r="C119" s="42" t="s">
-        <v>762</v>
+        <v>935</v>
       </c>
       <c r="D119" s="42" t="s">
-        <v>763</v>
+        <v>936</v>
       </c>
       <c r="E119" s="42" t="s">
-        <v>764</v>
+        <v>937</v>
       </c>
       <c r="F119" s="42" t="s">
-        <v>765</v>
+        <v>938</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="60" t="s">
-        <v>766</v>
+        <v>939</v>
       </c>
       <c r="B120" s="42" t="s">
-        <v>767</v>
+        <v>940</v>
       </c>
       <c r="C120" s="42" t="s">
-        <v>768</v>
+        <v>941</v>
       </c>
       <c r="D120" s="42" t="s">
-        <v>769</v>
+        <v>942</v>
       </c>
       <c r="E120" s="42" t="s">
-        <v>770</v>
+        <v>943</v>
       </c>
       <c r="F120" s="42" t="s">
-        <v>771</v>
+        <v>944</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="60" t="s">
-        <v>772</v>
+        <v>945</v>
       </c>
       <c r="B121" s="42" t="s">
-        <v>773</v>
+        <v>946</v>
       </c>
       <c r="C121" s="42" t="s">
-        <v>774</v>
+        <v>947</v>
       </c>
       <c r="D121" s="42" t="s">
-        <v>775</v>
+        <v>948</v>
       </c>
       <c r="E121" s="42" t="s">
-        <v>776</v>
+        <v>949</v>
       </c>
       <c r="F121" s="42" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="60" t="s">
-        <v>778</v>
+        <v>951</v>
       </c>
       <c r="B122" s="42" t="s">
-        <v>779</v>
+        <v>952</v>
       </c>
       <c r="C122" s="42" t="s">
-        <v>780</v>
+        <v>953</v>
       </c>
       <c r="D122" s="42" t="s">
-        <v>781</v>
+        <v>954</v>
       </c>
       <c r="E122" s="42" t="s">
-        <v>782</v>
+        <v>955</v>
       </c>
       <c r="F122" s="42" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="60" t="s">
-        <v>784</v>
+        <v>957</v>
       </c>
       <c r="B123" s="42" t="s">
-        <v>785</v>
+        <v>958</v>
       </c>
       <c r="C123" s="42" t="s">
-        <v>786</v>
+        <v>959</v>
       </c>
       <c r="D123" s="42" t="s">
-        <v>787</v>
+        <v>960</v>
       </c>
       <c r="E123" s="42" t="s">
-        <v>788</v>
+        <v>961</v>
       </c>
       <c r="F123" s="42" t="s">
-        <v>789</v>
+        <v>962</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="60" t="s">
-        <v>790</v>
+        <v>963</v>
       </c>
       <c r="B124" s="42" t="s">
-        <v>791</v>
+        <v>964</v>
       </c>
       <c r="C124" s="42" t="s">
-        <v>792</v>
+        <v>965</v>
       </c>
       <c r="D124" s="42" t="s">
-        <v>793</v>
+        <v>966</v>
       </c>
       <c r="E124" s="42" t="s">
-        <v>794</v>
+        <v>967</v>
       </c>
       <c r="F124" s="42" t="s">
-        <v>795</v>
+        <v>968</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="60" t="s">
-        <v>796</v>
+        <v>969</v>
       </c>
       <c r="B125" s="42" t="s">
-        <v>797</v>
+        <v>970</v>
       </c>
       <c r="C125" s="42" t="s">
-        <v>798</v>
+        <v>971</v>
       </c>
       <c r="D125" s="42" t="s">
-        <v>799</v>
+        <v>972</v>
       </c>
       <c r="E125" s="42" t="s">
-        <v>800</v>
+        <v>973</v>
       </c>
       <c r="F125" s="42" t="s">
-        <v>801</v>
+        <v>974</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11582,19 +13396,19 @@
         <v>404</v>
       </c>
       <c r="B126" s="42" t="s">
-        <v>802</v>
+        <v>975</v>
       </c>
       <c r="C126" s="42" t="s">
-        <v>803</v>
+        <v>976</v>
       </c>
       <c r="D126" s="42" t="s">
-        <v>804</v>
+        <v>977</v>
       </c>
       <c r="E126" s="42" t="s">
-        <v>805</v>
+        <v>978</v>
       </c>
       <c r="F126" s="42" t="s">
-        <v>806</v>
+        <v>979</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11602,19 +13416,19 @@
         <v>410</v>
       </c>
       <c r="B127" s="42" t="s">
-        <v>807</v>
+        <v>980</v>
       </c>
       <c r="C127" s="42" t="s">
-        <v>808</v>
+        <v>981</v>
       </c>
       <c r="D127" s="42" t="s">
-        <v>809</v>
+        <v>982</v>
       </c>
       <c r="E127" s="42" t="s">
-        <v>810</v>
+        <v>983</v>
       </c>
       <c r="F127" s="42" t="s">
-        <v>811</v>
+        <v>984</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11622,19 +13436,19 @@
         <v>416</v>
       </c>
       <c r="B128" s="42" t="s">
-        <v>812</v>
+        <v>985</v>
       </c>
       <c r="C128" s="42" t="s">
-        <v>813</v>
+        <v>986</v>
       </c>
       <c r="D128" s="42" t="s">
-        <v>814</v>
+        <v>987</v>
       </c>
       <c r="E128" s="42" t="s">
-        <v>815</v>
+        <v>988</v>
       </c>
       <c r="F128" s="42" t="s">
-        <v>816</v>
+        <v>989</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11642,39 +13456,39 @@
         <v>422</v>
       </c>
       <c r="B129" s="42" t="s">
-        <v>817</v>
+        <v>990</v>
       </c>
       <c r="C129" s="42" t="s">
-        <v>818</v>
+        <v>991</v>
       </c>
       <c r="D129" s="42" t="s">
-        <v>819</v>
+        <v>992</v>
       </c>
       <c r="E129" s="42" t="s">
-        <v>820</v>
+        <v>993</v>
       </c>
       <c r="F129" s="42" t="s">
-        <v>821</v>
+        <v>994</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="60" t="s">
-        <v>822</v>
+        <v>995</v>
       </c>
       <c r="B130" s="42" t="s">
-        <v>823</v>
+        <v>996</v>
       </c>
       <c r="C130" s="42" t="s">
-        <v>824</v>
+        <v>997</v>
       </c>
       <c r="D130" s="42" t="s">
-        <v>825</v>
+        <v>998</v>
       </c>
       <c r="E130" s="42" t="s">
-        <v>826</v>
+        <v>999</v>
       </c>
       <c r="F130" s="42" t="s">
-        <v>827</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -11682,8 +13496,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -11697,7 +13511,7 @@
   <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="79" width="36.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="86" width="36.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="35" width="90.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="35" width="77.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="35" width="65.07"/>
@@ -11706,23 +13520,23 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="80" t="s">
+      <c r="A1" s="87" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="80" t="s">
+      <c r="C1" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="80" t="s">
+      <c r="D1" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="80" t="s">
+      <c r="E1" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="81" t="s">
-        <v>828</v>
+      <c r="F1" s="88" t="s">
+        <v>1001</v>
       </c>
       <c r="G1" s="63"/>
       <c r="H1" s="63"/>
@@ -11731,18 +13545,18 @@
       <c r="K1" s="63"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83" t="s">
-        <v>829</v>
-      </c>
-      <c r="D2" s="83" t="s">
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D2" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="83" t="s">
-        <v>830</v>
-      </c>
-      <c r="F2" s="84"/>
+      <c r="E2" s="90" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F2" s="91"/>
       <c r="G2" s="63"/>
       <c r="H2" s="63"/>
       <c r="I2" s="63"/>
@@ -11750,20 +13564,20 @@
       <c r="K2" s="63"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="82"/>
-      <c r="B3" s="83" t="s">
-        <v>831</v>
-      </c>
-      <c r="C3" s="85" t="s">
-        <v>832</v>
-      </c>
-      <c r="D3" s="83" t="s">
+      <c r="A3" s="89"/>
+      <c r="B3" s="90" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C3" s="92" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D3" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="83" t="s">
-        <v>830</v>
-      </c>
-      <c r="F3" s="84"/>
+      <c r="E3" s="90" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F3" s="91"/>
       <c r="G3" s="63"/>
       <c r="H3" s="63"/>
       <c r="I3" s="63"/>
@@ -11771,20 +13585,20 @@
       <c r="K3" s="63"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83" t="s">
-        <v>833</v>
-      </c>
-      <c r="C4" s="85" t="s">
-        <v>834</v>
-      </c>
-      <c r="D4" s="83" t="s">
+      <c r="A4" s="89"/>
+      <c r="B4" s="90" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C4" s="92" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D4" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="83" t="s">
-        <v>835</v>
-      </c>
-      <c r="F4" s="84"/>
+      <c r="E4" s="90" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F4" s="91"/>
       <c r="G4" s="63"/>
       <c r="H4" s="63"/>
       <c r="I4" s="63"/>
@@ -11792,20 +13606,20 @@
       <c r="K4" s="63"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="82"/>
-      <c r="B5" s="83" t="s">
-        <v>836</v>
-      </c>
-      <c r="C5" s="85" t="s">
-        <v>832</v>
-      </c>
-      <c r="D5" s="83" t="s">
-        <v>835</v>
-      </c>
-      <c r="E5" s="83" t="s">
-        <v>830</v>
-      </c>
-      <c r="F5" s="84"/>
+      <c r="A5" s="89"/>
+      <c r="B5" s="90" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C5" s="92" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D5" s="90" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E5" s="90" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F5" s="91"/>
       <c r="G5" s="63"/>
       <c r="H5" s="63"/>
       <c r="I5" s="63"/>
@@ -11813,20 +13627,20 @@
       <c r="K5" s="63"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="82"/>
-      <c r="B6" s="83" t="s">
-        <v>837</v>
-      </c>
-      <c r="C6" s="85" t="s">
-        <v>838</v>
-      </c>
-      <c r="D6" s="83" t="s">
-        <v>835</v>
-      </c>
-      <c r="E6" s="85" t="s">
-        <v>839</v>
-      </c>
-      <c r="F6" s="84"/>
+      <c r="A6" s="89"/>
+      <c r="B6" s="90" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C6" s="92" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D6" s="90" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E6" s="92" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F6" s="91"/>
       <c r="G6" s="63"/>
       <c r="H6" s="63"/>
       <c r="I6" s="63"/>
@@ -11834,42 +13648,42 @@
       <c r="K6" s="63"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="82" t="s">
-        <v>840</v>
-      </c>
-      <c r="B7" s="86" t="s">
-        <v>841</v>
-      </c>
-      <c r="C7" s="87" t="s">
-        <v>842</v>
-      </c>
-      <c r="D7" s="87" t="s">
-        <v>843</v>
-      </c>
-      <c r="E7" s="87" t="s">
-        <v>844</v>
-      </c>
-      <c r="F7" s="84"/>
+      <c r="A7" s="89" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B7" s="93" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C7" s="94" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D7" s="94" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E7" s="94" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F7" s="91"/>
       <c r="G7" s="64"/>
       <c r="H7" s="64"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="82" t="s">
+      <c r="A8" s="89" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="86" t="s">
-        <v>845</v>
-      </c>
-      <c r="C8" s="87" t="s">
-        <v>846</v>
-      </c>
-      <c r="D8" s="87" t="s">
-        <v>843</v>
-      </c>
-      <c r="E8" s="87" t="s">
-        <v>847</v>
-      </c>
-      <c r="F8" s="84"/>
+      <c r="B8" s="93" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C8" s="94" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D8" s="94" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E8" s="94" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F8" s="91"/>
       <c r="G8" s="63"/>
       <c r="H8" s="63"/>
       <c r="I8" s="63"/>
@@ -11877,22 +13691,22 @@
       <c r="K8" s="63"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="82" t="s">
+      <c r="A9" s="89" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="86" t="s">
-        <v>848</v>
-      </c>
-      <c r="C9" s="87" t="s">
-        <v>842</v>
-      </c>
-      <c r="D9" s="87" t="s">
-        <v>847</v>
-      </c>
-      <c r="E9" s="87" t="s">
-        <v>849</v>
-      </c>
-      <c r="F9" s="84"/>
+      <c r="B9" s="93" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C9" s="94" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D9" s="94" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E9" s="94" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F9" s="91"/>
       <c r="G9" s="63"/>
       <c r="H9" s="63"/>
       <c r="I9" s="63"/>
@@ -11900,20 +13714,20 @@
       <c r="K9" s="63"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="88" t="s">
+      <c r="A10" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="89" t="s">
-        <v>850</v>
-      </c>
-      <c r="C10" s="90" t="s">
-        <v>851</v>
-      </c>
-      <c r="D10" s="90" t="s">
-        <v>843</v>
-      </c>
-      <c r="E10" s="90" t="s">
-        <v>852</v>
+      <c r="B10" s="96" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C10" s="97" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D10" s="97" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E10" s="97" t="s">
+        <v>1025</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="63"/>
@@ -11923,22 +13737,22 @@
       <c r="K10" s="63"/>
     </row>
     <row r="11" customFormat="false" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="91" t="s">
+      <c r="A11" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="92" t="s">
-        <v>853</v>
-      </c>
-      <c r="C11" s="93" t="s">
-        <v>842</v>
-      </c>
-      <c r="D11" s="93" t="s">
-        <v>852</v>
-      </c>
-      <c r="E11" s="93" t="s">
-        <v>854</v>
-      </c>
-      <c r="F11" s="94"/>
+      <c r="B11" s="99" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C11" s="100" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D11" s="100" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E11" s="100" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F11" s="101"/>
       <c r="G11" s="63"/>
       <c r="H11" s="63"/>
       <c r="I11" s="63"/>
@@ -11946,21 +13760,21 @@
       <c r="K11" s="63"/>
     </row>
     <row r="12" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="91" t="s">
+      <c r="A12" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="93" t="s">
-        <v>855</v>
-      </c>
-      <c r="C12" s="93" t="s">
-        <v>856</v>
-      </c>
-      <c r="D12" s="93" t="s">
-        <v>857</v>
-      </c>
-      <c r="E12" s="93"/>
-      <c r="F12" s="95" t="s">
-        <v>858</v>
+      <c r="B12" s="100" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C12" s="100" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D12" s="100" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E12" s="100"/>
+      <c r="F12" s="102" t="s">
+        <v>1031</v>
       </c>
       <c r="G12" s="63"/>
       <c r="H12" s="63"/>
@@ -11969,20 +13783,20 @@
       <c r="K12" s="63"/>
     </row>
     <row r="13" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="91" t="s">
+      <c r="A13" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="93" t="s">
-        <v>859</v>
-      </c>
-      <c r="C13" s="93" t="s">
-        <v>860</v>
-      </c>
-      <c r="D13" s="93" t="s">
-        <v>861</v>
-      </c>
-      <c r="E13" s="93"/>
-      <c r="F13" s="95"/>
+      <c r="B13" s="100" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C13" s="100" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D13" s="100" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E13" s="100"/>
+      <c r="F13" s="102"/>
       <c r="G13" s="63"/>
       <c r="H13" s="63"/>
       <c r="I13" s="63"/>
@@ -11990,12 +13804,12 @@
       <c r="K13" s="63"/>
     </row>
     <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="96"/>
-      <c r="B14" s="97"/>
-      <c r="C14" s="97"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="97"/>
-      <c r="F14" s="98"/>
+      <c r="A14" s="103"/>
+      <c r="B14" s="104"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="105"/>
       <c r="G14" s="63"/>
       <c r="H14" s="63"/>
       <c r="I14" s="63"/>
@@ -12003,12 +13817,12 @@
       <c r="K14" s="63"/>
     </row>
     <row r="15" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="99"/>
-      <c r="B15" s="100"/>
-      <c r="C15" s="100"/>
-      <c r="D15" s="100"/>
-      <c r="E15" s="100"/>
-      <c r="F15" s="101"/>
+      <c r="A15" s="106"/>
+      <c r="B15" s="107"/>
+      <c r="C15" s="107"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="107"/>
+      <c r="F15" s="108"/>
       <c r="G15" s="63"/>
       <c r="H15" s="63"/>
       <c r="I15" s="63"/>
@@ -12016,22 +13830,22 @@
       <c r="K15" s="63"/>
     </row>
     <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="88" t="s">
+      <c r="A16" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="90" t="s">
-        <v>862</v>
-      </c>
-      <c r="C16" s="90" t="s">
-        <v>846</v>
-      </c>
-      <c r="D16" s="90" t="s">
-        <v>863</v>
-      </c>
-      <c r="E16" s="90" t="s">
-        <v>864</v>
-      </c>
-      <c r="F16" s="102"/>
+      <c r="B16" s="97" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C16" s="97" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D16" s="97" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E16" s="97" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F16" s="109"/>
       <c r="G16" s="63"/>
       <c r="H16" s="63"/>
       <c r="I16" s="63"/>
@@ -12039,22 +13853,22 @@
       <c r="K16" s="63"/>
     </row>
     <row r="17" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="93" t="s">
-        <v>865</v>
-      </c>
-      <c r="C17" s="93" t="s">
-        <v>842</v>
-      </c>
-      <c r="D17" s="93" t="s">
-        <v>864</v>
-      </c>
-      <c r="E17" s="93" t="s">
-        <v>866</v>
-      </c>
-      <c r="F17" s="95"/>
+      <c r="B17" s="100" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C17" s="100" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D17" s="100" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E17" s="100" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F17" s="102"/>
       <c r="G17" s="63"/>
       <c r="H17" s="63"/>
       <c r="I17" s="63"/>
@@ -12062,21 +13876,21 @@
       <c r="K17" s="63"/>
     </row>
     <row r="18" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="103" t="s">
+      <c r="A18" s="110" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="104" t="s">
-        <v>867</v>
-      </c>
-      <c r="C18" s="104" t="s">
-        <v>856</v>
-      </c>
-      <c r="D18" s="104" t="s">
-        <v>868</v>
-      </c>
-      <c r="E18" s="104"/>
-      <c r="F18" s="105" t="s">
-        <v>869</v>
+      <c r="B18" s="111" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C18" s="111" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D18" s="111" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E18" s="111"/>
+      <c r="F18" s="112" t="s">
+        <v>1042</v>
       </c>
       <c r="G18" s="63"/>
       <c r="H18" s="63"/>
@@ -12085,20 +13899,20 @@
       <c r="K18" s="63"/>
     </row>
     <row r="19" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="96" t="s">
+      <c r="A19" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="97" t="s">
-        <v>870</v>
-      </c>
-      <c r="C19" s="97" t="s">
-        <v>860</v>
-      </c>
-      <c r="D19" s="97" t="s">
-        <v>871</v>
-      </c>
-      <c r="E19" s="97"/>
-      <c r="F19" s="98"/>
+      <c r="B19" s="104" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C19" s="104" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D19" s="104" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E19" s="104"/>
+      <c r="F19" s="105"/>
       <c r="G19" s="63"/>
       <c r="H19" s="63"/>
       <c r="I19" s="63"/>
@@ -12106,12 +13920,12 @@
       <c r="K19" s="63"/>
     </row>
     <row r="20" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="96"/>
-      <c r="B20" s="97"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="97"/>
-      <c r="F20" s="98"/>
+      <c r="A20" s="103"/>
+      <c r="B20" s="104"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="105"/>
       <c r="G20" s="63"/>
       <c r="H20" s="63"/>
       <c r="I20" s="63"/>
@@ -12119,12 +13933,12 @@
       <c r="K20" s="63"/>
     </row>
     <row r="21" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="106"/>
-      <c r="B21" s="107"/>
-      <c r="C21" s="107"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="108"/>
+      <c r="A21" s="113"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="115"/>
       <c r="G21" s="63"/>
       <c r="H21" s="63"/>
       <c r="I21" s="63"/>
@@ -12132,20 +13946,20 @@
       <c r="K21" s="63"/>
     </row>
     <row r="22" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="88" t="s">
+      <c r="A22" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="89" t="s">
-        <v>872</v>
-      </c>
-      <c r="C22" s="90" t="s">
-        <v>851</v>
-      </c>
-      <c r="D22" s="90" t="s">
-        <v>843</v>
-      </c>
-      <c r="E22" s="90" t="s">
-        <v>873</v>
+      <c r="B22" s="96" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C22" s="97" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D22" s="97" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E22" s="97" t="s">
+        <v>1046</v>
       </c>
       <c r="F22" s="24"/>
       <c r="G22" s="63"/>
@@ -12155,22 +13969,22 @@
       <c r="K22" s="63"/>
     </row>
     <row r="23" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="91" t="s">
+      <c r="A23" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="92" t="s">
-        <v>874</v>
-      </c>
-      <c r="C23" s="93" t="s">
-        <v>842</v>
-      </c>
-      <c r="D23" s="93" t="s">
-        <v>873</v>
-      </c>
-      <c r="E23" s="93" t="s">
-        <v>875</v>
-      </c>
-      <c r="F23" s="94"/>
+      <c r="B23" s="99" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C23" s="100" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D23" s="100" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E23" s="100" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F23" s="101"/>
       <c r="G23" s="63"/>
       <c r="H23" s="63"/>
       <c r="I23" s="63"/>
@@ -12178,21 +13992,21 @@
       <c r="K23" s="63"/>
     </row>
     <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="103" t="s">
+      <c r="A24" s="110" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="104" t="s">
-        <v>876</v>
-      </c>
-      <c r="C24" s="104" t="s">
-        <v>856</v>
-      </c>
-      <c r="D24" s="104" t="s">
-        <v>877</v>
-      </c>
-      <c r="E24" s="104"/>
-      <c r="F24" s="105" t="s">
-        <v>878</v>
+      <c r="B24" s="111" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C24" s="111" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D24" s="111" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E24" s="111"/>
+      <c r="F24" s="112" t="s">
+        <v>1051</v>
       </c>
       <c r="G24" s="63"/>
       <c r="H24" s="63"/>
@@ -12201,20 +14015,20 @@
       <c r="K24" s="63"/>
     </row>
     <row r="25" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="96" t="s">
+      <c r="A25" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="97" t="s">
-        <v>879</v>
-      </c>
-      <c r="C25" s="97" t="s">
-        <v>860</v>
-      </c>
-      <c r="D25" s="97" t="s">
-        <v>880</v>
-      </c>
-      <c r="E25" s="97"/>
-      <c r="F25" s="98"/>
+      <c r="B25" s="104" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C25" s="104" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D25" s="104" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E25" s="104"/>
+      <c r="F25" s="105"/>
       <c r="G25" s="63"/>
       <c r="H25" s="63"/>
       <c r="I25" s="63"/>
@@ -12222,12 +14036,12 @@
       <c r="K25" s="63"/>
     </row>
     <row r="26" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="96"/>
-      <c r="B26" s="97"/>
-      <c r="C26" s="97"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="97"/>
-      <c r="F26" s="98"/>
+      <c r="A26" s="103"/>
+      <c r="B26" s="104"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="104"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="105"/>
       <c r="G26" s="63"/>
       <c r="H26" s="63"/>
       <c r="I26" s="63"/>
@@ -12235,12 +14049,12 @@
       <c r="K26" s="63"/>
     </row>
     <row r="27" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="99"/>
-      <c r="B27" s="100"/>
-      <c r="C27" s="100"/>
-      <c r="D27" s="100"/>
-      <c r="E27" s="100"/>
-      <c r="F27" s="101"/>
+      <c r="A27" s="106"/>
+      <c r="B27" s="107"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="107"/>
+      <c r="F27" s="108"/>
       <c r="G27" s="63"/>
       <c r="H27" s="63"/>
       <c r="I27" s="63"/>
@@ -12248,22 +14062,22 @@
       <c r="K27" s="63"/>
     </row>
     <row r="28" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="88" t="s">
+      <c r="A28" s="95" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="90" t="s">
-        <v>881</v>
-      </c>
-      <c r="C28" s="90" t="s">
-        <v>846</v>
-      </c>
-      <c r="D28" s="90" t="s">
-        <v>882</v>
-      </c>
-      <c r="E28" s="90" t="s">
-        <v>883</v>
-      </c>
-      <c r="F28" s="102"/>
+      <c r="B28" s="97" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C28" s="97" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D28" s="97" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E28" s="97" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F28" s="109"/>
       <c r="G28" s="63"/>
       <c r="H28" s="63"/>
       <c r="I28" s="63"/>
@@ -12271,22 +14085,22 @@
       <c r="K28" s="63"/>
     </row>
     <row r="29" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="91" t="s">
+      <c r="A29" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="93" t="s">
-        <v>884</v>
-      </c>
-      <c r="C29" s="93" t="s">
-        <v>842</v>
-      </c>
-      <c r="D29" s="93" t="s">
-        <v>883</v>
-      </c>
-      <c r="E29" s="93" t="s">
-        <v>885</v>
-      </c>
-      <c r="F29" s="95"/>
+      <c r="B29" s="100" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C29" s="100" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D29" s="100" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E29" s="100" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F29" s="102"/>
       <c r="G29" s="63"/>
       <c r="H29" s="63"/>
       <c r="I29" s="63"/>
@@ -12294,21 +14108,21 @@
       <c r="K29" s="63"/>
     </row>
     <row r="30" customFormat="false" ht="199" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="103" t="s">
+      <c r="A30" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="104" t="s">
-        <v>886</v>
-      </c>
-      <c r="C30" s="104" t="s">
-        <v>856</v>
-      </c>
-      <c r="D30" s="104" t="s">
-        <v>887</v>
-      </c>
-      <c r="E30" s="104"/>
-      <c r="F30" s="105" t="s">
-        <v>888</v>
+      <c r="B30" s="111" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C30" s="111" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D30" s="111" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E30" s="111"/>
+      <c r="F30" s="112" t="s">
+        <v>1061</v>
       </c>
       <c r="G30" s="63"/>
       <c r="H30" s="63"/>
@@ -12317,20 +14131,20 @@
       <c r="K30" s="63"/>
     </row>
     <row r="31" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="96" t="s">
+      <c r="A31" s="103" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="97" t="s">
-        <v>889</v>
-      </c>
-      <c r="C31" s="97" t="s">
-        <v>860</v>
-      </c>
-      <c r="D31" s="97" t="s">
-        <v>890</v>
-      </c>
-      <c r="E31" s="97"/>
-      <c r="F31" s="98"/>
+      <c r="B31" s="104" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C31" s="104" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D31" s="104" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E31" s="104"/>
+      <c r="F31" s="105"/>
       <c r="G31" s="63"/>
       <c r="H31" s="63"/>
       <c r="I31" s="63"/>
@@ -12338,12 +14152,12 @@
       <c r="K31" s="63"/>
     </row>
     <row r="32" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="96"/>
-      <c r="B32" s="97"/>
-      <c r="C32" s="97"/>
-      <c r="D32" s="97"/>
-      <c r="E32" s="97"/>
-      <c r="F32" s="98"/>
+      <c r="A32" s="103"/>
+      <c r="B32" s="104"/>
+      <c r="C32" s="104"/>
+      <c r="D32" s="104"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="105"/>
       <c r="G32" s="63"/>
       <c r="H32" s="63"/>
       <c r="I32" s="63"/>
@@ -12351,12 +14165,12 @@
       <c r="K32" s="63"/>
     </row>
     <row r="33" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="99"/>
-      <c r="B33" s="109"/>
-      <c r="C33" s="109"/>
-      <c r="D33" s="109"/>
-      <c r="E33" s="109"/>
-      <c r="F33" s="110"/>
+      <c r="A33" s="106"/>
+      <c r="B33" s="116"/>
+      <c r="C33" s="116"/>
+      <c r="D33" s="116"/>
+      <c r="E33" s="116"/>
+      <c r="F33" s="117"/>
       <c r="G33" s="63"/>
       <c r="H33" s="63"/>
       <c r="I33" s="63"/>
@@ -12431,8 +14245,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -12458,7 +14272,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.47"/>
   </cols>
   <sheetData>
-    <row r="1" s="112" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="119" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="65" t="s">
         <v>68</v>
       </c>
@@ -12466,13 +14280,13 @@
         <v>69</v>
       </c>
       <c r="C1" s="66" t="s">
-        <v>891</v>
+        <v>1064</v>
       </c>
       <c r="D1" s="66" t="s">
         <v>71</v>
       </c>
       <c r="E1" s="66" t="s">
-        <v>892</v>
+        <v>1065</v>
       </c>
       <c r="F1" s="66" t="s">
         <v>25</v>
@@ -12483,7 +14297,7 @@
       <c r="H1" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="118" t="s">
         <v>58</v>
       </c>
       <c r="XFC1" s="1"/>
@@ -12491,7 +14305,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>893</v>
+        <v>1066</v>
       </c>
       <c r="B2" s="41" t="n">
         <v>0</v>
@@ -12521,7 +14335,7 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>894</v>
+        <v>1067</v>
       </c>
       <c r="B3" s="41" t="n">
         <v>1</v>
@@ -12551,7 +14365,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>895</v>
+        <v>1068</v>
       </c>
       <c r="B4" s="41" t="n">
         <v>2</v>
@@ -12581,7 +14395,7 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>896</v>
+        <v>1069</v>
       </c>
       <c r="B5" s="41" t="n">
         <v>3</v>
@@ -12641,7 +14455,7 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>897</v>
+        <v>1070</v>
       </c>
       <c r="B7" s="41" t="n">
         <v>5</v>
@@ -12671,7 +14485,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>898</v>
+        <v>1071</v>
       </c>
       <c r="B8" s="41" t="n">
         <v>6</v>
@@ -12731,7 +14545,7 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="40" t="s">
-        <v>899</v>
+        <v>1072</v>
       </c>
       <c r="B10" s="41" t="n">
         <v>8</v>
@@ -12761,7 +14575,7 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="40" t="s">
-        <v>900</v>
+        <v>1073</v>
       </c>
       <c r="B11" s="41" t="n">
         <v>9</v>
@@ -12791,7 +14605,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>901</v>
+        <v>1074</v>
       </c>
       <c r="B12" s="41" t="n">
         <v>10</v>
@@ -12821,7 +14635,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="40" t="s">
-        <v>902</v>
+        <v>1075</v>
       </c>
       <c r="B13" s="41" t="n">
         <v>11</v>
@@ -12851,7 +14665,7 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="s">
-        <v>903</v>
+        <v>1076</v>
       </c>
       <c r="B14" s="41" t="n">
         <v>12</v>
@@ -12880,7 +14694,7 @@
       <c r="J14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="113" t="s">
+      <c r="A15" s="120" t="s">
         <v>493</v>
       </c>
       <c r="B15" s="48" t="n">
@@ -13244,7 +15058,7 @@
       <c r="J38" s="42"/>
       <c r="K38" s="42"/>
     </row>
-    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
         <v>20</v>
       </c>
@@ -13713,7 +15527,7 @@
       <c r="J69" s="42"/>
       <c r="K69" s="42"/>
     </row>
-    <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
         <v>17</v>
       </c>
@@ -13747,7 +15561,7 @@
       <c r="J71" s="42"/>
       <c r="K71" s="42"/>
     </row>
-    <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
         <v>20</v>
       </c>
@@ -14162,8 +15976,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
